--- a/src/attributions/attributions_saliency_traj_101.xlsx
+++ b/src/attributions/attributions_saliency_traj_101.xlsx
@@ -999,1709 +999,1709 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0006662961095571518</v>
+        <v>0.04461202770471573</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3257189095020294</v>
+        <v>1.626091003417969</v>
       </c>
       <c r="C2" t="n">
-        <v>0.012267273850739</v>
+        <v>0.505064845085144</v>
       </c>
       <c r="D2" t="n">
-        <v>0.264300525188446</v>
+        <v>0.9861005544662476</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04462730512022972</v>
+        <v>0.3297421336174011</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07047152519226074</v>
+        <v>0.1828428357839584</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03664280474185944</v>
+        <v>0.3575728535652161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0264836922287941</v>
+        <v>0.1976602673530579</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02221678197383881</v>
+        <v>0.122508779168129</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01547925267368555</v>
+        <v>0.4260213375091553</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2774257361888885</v>
+        <v>1.599897623062134</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004209416918456554</v>
+        <v>0.4903452098369598</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2432319670915604</v>
+        <v>1.526984453201294</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05309776589274406</v>
+        <v>0.5750662684440613</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06283453851938248</v>
+        <v>0.1507649421691895</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0157652460038662</v>
+        <v>0.368090033531189</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03120752424001694</v>
+        <v>0.02467871457338333</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02394842356443405</v>
+        <v>0.02299845777451992</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01557696796953678</v>
+        <v>0.04901234060525894</v>
       </c>
       <c r="T2" t="n">
-        <v>0.04514051228761673</v>
+        <v>0.3453571498394012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01535364240407944</v>
+        <v>0.1393029391765594</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01727460883557796</v>
+        <v>0.0846836194396019</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02718440257012844</v>
+        <v>0.04533487185835838</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0419013723731041</v>
+        <v>0.239033579826355</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04331827536225319</v>
+        <v>0.0496409609913826</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01060635223984718</v>
+        <v>0.1008039116859436</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02325232140719891</v>
+        <v>0.2749019861221313</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04186674579977989</v>
+        <v>0.2345187067985535</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05406965687870979</v>
+        <v>0.2065898925065994</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0002788379788398743</v>
+        <v>0.1489977240562439</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001213267794810236</v>
+        <v>0.4081824123859406</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0139822643250227</v>
+        <v>0.03696019202470779</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.01610331609845161</v>
+        <v>0.09551788866519928</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.008641762658953667</v>
+        <v>0.1425816416740417</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.005249957554042339</v>
+        <v>0.02099409326910973</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008144982159137726</v>
+        <v>0.003118441440165043</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01783313229680061</v>
+        <v>0.01259982585906982</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03317851945757866</v>
+        <v>0.6769243478775024</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001136534381657839</v>
+        <v>0.03208418935537338</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.006606697104871273</v>
+        <v>0.07831492274999619</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.005688949953764677</v>
+        <v>0.6206262707710266</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.02102817967534065</v>
+        <v>0.3111637532711029</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.01176376733928919</v>
+        <v>0.07205082476139069</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01914123073220253</v>
+        <v>0.02680512331426144</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.02497721090912819</v>
+        <v>0.002675270661711693</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02692523412406445</v>
+        <v>0.1065273135900497</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2167764008045197</v>
+        <v>1.294655323028564</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.03654546290636063</v>
+        <v>0.1594884991645813</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1016209200024605</v>
+        <v>0.4189132153987885</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01146325469017029</v>
+        <v>0.5135302543640137</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.01539079658687115</v>
+        <v>0.00118660181760788</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01465057022869587</v>
+        <v>0.01967238821089268</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.02615480124950409</v>
+        <v>0.09287735819816589</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0316343642771244</v>
+        <v>0.1807209253311157</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.007214700803160667</v>
+        <v>0.001735379919409752</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.03935373574495316</v>
+        <v>0.3431254029273987</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.06893511861562729</v>
+        <v>0.4388558268547058</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.03908882662653923</v>
+        <v>0.1367021203041077</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.05514751374721527</v>
+        <v>0.08277974277734756</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.007605141960084438</v>
+        <v>0.1383922100067139</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.04447026923298836</v>
+        <v>0.1263982951641083</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.03978212922811508</v>
+        <v>0.02285167947411537</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.03166499733924866</v>
+        <v>0.3006510436534882</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.05406158417463303</v>
+        <v>0.0496092177927494</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.04760994389653206</v>
+        <v>0.3892471790313721</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.01201318483799696</v>
+        <v>0.07911349833011627</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.00316180381923914</v>
+        <v>0.0151984840631485</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.002764587057754397</v>
+        <v>0.02248419262468815</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01417767163366079</v>
+        <v>0.121830590069294</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.006335421465337276</v>
+        <v>0.07206865400075912</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.01174110546708107</v>
+        <v>0.02572193183004856</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0201257485896349</v>
+        <v>0.0493808425962925</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.02544182166457176</v>
+        <v>0.05112333223223686</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1179923191666603</v>
+        <v>0.8372939825057983</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.007659859955310822</v>
+        <v>0.03372505307197571</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04530412703752518</v>
+        <v>0.425124853849411</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.01395363081246614</v>
+        <v>0.1871104538440704</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0006038343999534845</v>
+        <v>0.3114421367645264</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.009934678673744202</v>
+        <v>0.1131675541400909</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.005998698994517326</v>
+        <v>0.009236590936779976</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.01599160023033619</v>
+        <v>0.1767659485340118</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.003827064763754606</v>
+        <v>0.06411217898130417</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0466545894742012</v>
+        <v>0.5333130359649658</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.01723799481987953</v>
+        <v>0.1362275332212448</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.04568234086036682</v>
+        <v>0.3159716129302979</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01719163917005062</v>
+        <v>0.03953232243657112</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.01277622766792774</v>
+        <v>0.02594370953738689</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.01099088508635759</v>
+        <v>0.002200622111558914</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0002795038744807243</v>
+        <v>0.03278592973947525</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.006164123769849539</v>
+        <v>0.07087701559066772</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.05088012292981148</v>
+        <v>0.238608717918396</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.003020158503204584</v>
+        <v>0.5631155967712402</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.008043279871344566</v>
+        <v>0.1606159061193466</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.04278809577226639</v>
+        <v>0.6046173572540283</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.05617953091859818</v>
+        <v>0.2578910291194916</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.055716373026371</v>
+        <v>0.2101259678602219</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.04279704391956329</v>
+        <v>0.06922055780887604</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.06339088827371597</v>
+        <v>0.04994634911417961</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.009162021800875664</v>
+        <v>0.1266998648643494</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0005137657281011343</v>
+        <v>0.1243320032954216</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.05621202290058136</v>
+        <v>0.55804443359375</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01990317925810814</v>
+        <v>0.0873945951461792</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.05455198511481285</v>
+        <v>0.3249342739582062</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01595174707472324</v>
+        <v>0.0326310321688652</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0187893733382225</v>
+        <v>0.001524079591035843</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.01200017239898443</v>
+        <v>0.01913885027170181</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.000799473375082016</v>
+        <v>0.01493536494672298</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.003503507934510708</v>
+        <v>0.1140201687812805</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0119507685303688</v>
+        <v>0.237455278635025</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.04387247562408447</v>
+        <v>0.5038306713104248</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.03913474455475807</v>
+        <v>0.05935315787792206</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.08616733551025391</v>
+        <v>0.509119987487793</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05117765814065933</v>
+        <v>0.2035520970821381</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.05128319561481476</v>
+        <v>0.6456206440925598</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.03419940918684006</v>
+        <v>0.03750402480363846</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.01191182620823383</v>
+        <v>0.3864589631557465</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.01196205522865057</v>
+        <v>0.00741889700293541</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.004508974030613899</v>
+        <v>0.007230725139379501</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02291362173855305</v>
+        <v>0.1852176487445831</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.03231518343091011</v>
+        <v>0.05813740193843842</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.02109948359429836</v>
+        <v>0.2586981654167175</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0161735974252224</v>
+        <v>0.3122125864028931</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.02687602490186691</v>
+        <v>0.005583243444561958</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.001272538211196661</v>
+        <v>0.1786251664161682</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.01059486344456673</v>
+        <v>0.1759244203567505</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.01983651518821716</v>
+        <v>0.3989575207233429</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.01847823336720467</v>
+        <v>0.01939095743000507</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.004549819976091385</v>
+        <v>0.2050691694021225</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.05434515327215195</v>
+        <v>0.04146202653646469</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.02549276500940323</v>
+        <v>0.3486331701278687</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.002405722159892321</v>
+        <v>0.009233869612216949</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.006434340961277485</v>
+        <v>0.3657553791999817</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01295348163694143</v>
+        <v>0.01603778451681137</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.005160789005458355</v>
+        <v>0.6243559718132019</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0008927229791879654</v>
+        <v>0.3363690376281738</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.006235488224774599</v>
+        <v>0.169794887304306</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.06527931243181229</v>
+        <v>0.5287652015686035</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.01119647268205881</v>
+        <v>0.01415076106786728</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0510864332318306</v>
+        <v>0.1795946210622787</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03301114961504936</v>
+        <v>0.06868383288383484</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.007650306448340416</v>
+        <v>0.164945051074028</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.01090377569198608</v>
+        <v>0.003386840224266052</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.01004400569945574</v>
+        <v>0.04324644058942795</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.01153400912880898</v>
+        <v>0.04106445983052254</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.002863880479708314</v>
+        <v>0.1010885015130043</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.03429486602544785</v>
+        <v>0.4707491993904114</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.03871800377964973</v>
+        <v>0.167516827583313</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03973837941884995</v>
+        <v>0.1947813630104065</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0458884984254837</v>
+        <v>0.17220838367939</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.07513438910245895</v>
+        <v>0.2067079097032547</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.01833014003932476</v>
+        <v>0.1571704596281052</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.005530040245503187</v>
+        <v>0.06052698567509651</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.01224963180720806</v>
+        <v>0.1315582692623138</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.004057008307427168</v>
+        <v>0.08931931853294373</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.05794268101453781</v>
+        <v>0.6266295313835144</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0132160559296608</v>
+        <v>0.1019704192876816</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.04597890377044678</v>
+        <v>0.390290379524231</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02104336209595203</v>
+        <v>0.02186367474496365</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.02074436098337173</v>
+        <v>0.047140933573246</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0136678759008646</v>
+        <v>0.03124692849814892</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.002029385417699814</v>
+        <v>0.06752319633960724</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.004476184025406837</v>
+        <v>0.09696949273347855</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01170238759368658</v>
+        <v>0.02071666717529297</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01873032189905643</v>
+        <v>0.2192125022411346</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.009815538302063942</v>
+        <v>0.3170097768306732</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.005166089627891779</v>
+        <v>0.07054069638252258</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.002304891590029001</v>
+        <v>0.09574110805988312</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.002131612040102482</v>
+        <v>0.1091345623135567</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.014254798181355</v>
+        <v>0.02618129178881645</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.005916289053857327</v>
+        <v>0.2267912626266479</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.01843571662902832</v>
+        <v>0.299733579158783</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.02055580541491508</v>
+        <v>0.009406708180904388</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.00859173946082592</v>
+        <v>0.6312112808227539</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.004154589958488941</v>
+        <v>0.3278196156024933</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.02222056686878204</v>
+        <v>0.5383363962173462</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.03189427405595779</v>
+        <v>0.3120318949222565</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.001281461678445339</v>
+        <v>0.02292058616876602</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.009596280753612518</v>
+        <v>0.02933303453028202</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0008138883858919144</v>
+        <v>0.1256300210952759</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.02177046053111553</v>
+        <v>0.532747209072113</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.02947100251913071</v>
+        <v>0.08513514697551727</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.002308705355972052</v>
+        <v>0.4101139008998871</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.01289283484220505</v>
+        <v>0.1186929643154144</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.004848984535783529</v>
+        <v>0.2086988836526871</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.03158136084675789</v>
+        <v>0.6057834029197693</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.01577265560626984</v>
+        <v>0.009361927397549152</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.07153224945068359</v>
+        <v>0.2755287289619446</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.002933956449851394</v>
+        <v>0.1286507397890091</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.02391260303556919</v>
+        <v>0.0105453273281455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03645465895533562</v>
+        <v>0.252443253993988</v>
       </c>
       <c r="B3" t="n">
-        <v>1.928931832313538</v>
+        <v>0.7695663571357727</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0325884073972702</v>
+        <v>0.04953432828187943</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6277582049369812</v>
+        <v>0.08464835584163666</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4147432446479797</v>
+        <v>0.184018462896347</v>
       </c>
       <c r="F3" t="n">
-        <v>1.303420066833496</v>
+        <v>0.3597699105739594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1258684694766998</v>
+        <v>0.04774938151240349</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5066913962364197</v>
+        <v>0.1689787805080414</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1005213335156441</v>
+        <v>0.01472362224012613</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4164179563522339</v>
+        <v>0.2367744594812393</v>
       </c>
       <c r="K3" t="n">
-        <v>1.563593149185181</v>
+        <v>0.9185901284217834</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09411387890577316</v>
+        <v>0.03916886821389198</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03894579410553</v>
+        <v>0.2501614689826965</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1920171976089478</v>
+        <v>0.02836033701896667</v>
       </c>
       <c r="O3" t="n">
-        <v>1.131273984909058</v>
+        <v>0.4101191163063049</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3043051064014435</v>
+        <v>0.002460436895489693</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5139217376708984</v>
+        <v>0.06244075670838356</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1195594370365143</v>
+        <v>0.03540797531604767</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3642145693302155</v>
+        <v>0.01269623264670372</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2401308119297028</v>
+        <v>0.1476000845432281</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02933984063565731</v>
+        <v>0.01650440320372581</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02431226149201393</v>
+        <v>0.1691693961620331</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2111581414937973</v>
+        <v>0.08805441856384277</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2298350036144257</v>
+        <v>0.06122179329395294</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003468595445156097</v>
+        <v>0.03560145944356918</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004299715161323547</v>
+        <v>0.1756707429885864</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08350834250450134</v>
+        <v>0.002582410350441933</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1252997219562531</v>
+        <v>0.08951035141944885</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3742226362228394</v>
+        <v>0.1001851260662079</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2383117377758026</v>
+        <v>0.000299450010061264</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01065816730260849</v>
+        <v>0.2039991766214371</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1523391604423523</v>
+        <v>0.189007967710495</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1433929651975632</v>
+        <v>0.01436770707368851</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2282775342464447</v>
+        <v>0.05915419012308121</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.420747816562653e-05</v>
+        <v>0.391210526227951</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1004323959350586</v>
+        <v>0.1082169264554977</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0005389600992202759</v>
+        <v>0.01909921132028103</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2421018779277802</v>
+        <v>0.1456120014190674</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1787494122982025</v>
+        <v>0.1054431572556496</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.07505667209625244</v>
+        <v>0.01827385649085045</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.27623650431633</v>
+        <v>0.2040799707174301</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4259024560451508</v>
+        <v>0.1225229054689407</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.01825400441884995</v>
+        <v>0.08979081362485886</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1891355812549591</v>
+        <v>0.257622241973877</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1932244002819061</v>
+        <v>0.02712645009160042</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1597903817892075</v>
+        <v>0.101492203772068</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.423157334327698</v>
+        <v>0.721449077129364</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1435444504022598</v>
+        <v>0.06066660210490227</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.005117543041706085</v>
+        <v>0.04279779642820358</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4672462642192841</v>
+        <v>0.07940410077571869</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.041540026664734</v>
+        <v>0.4438912570476532</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1351587176322937</v>
+        <v>0.002555079758167267</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.08652570843696594</v>
+        <v>0.02003398723900318</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.315005749464035</v>
+        <v>0.03984972089529037</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1221515014767647</v>
+        <v>0.00528986006975174</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.6304505467414856</v>
+        <v>0.09852615743875504</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.3214818835258484</v>
+        <v>0.08379459381103516</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2274883687496185</v>
+        <v>0.09938351809978485</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0730786919593811</v>
+        <v>0.05083020403981209</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.02249390631914139</v>
+        <v>0.04643680155277252</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.05722134560346603</v>
+        <v>0.07397009432315826</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.08796662837266922</v>
+        <v>0.1398296058177948</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1864555031061172</v>
+        <v>0.1246841698884964</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1327403634786606</v>
+        <v>0.08437664061784744</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.09307175129652023</v>
+        <v>0.05445738136768341</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.02134572900831699</v>
+        <v>0.03744033724069595</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1588204801082611</v>
+        <v>0.03415574505925179</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2536043524742126</v>
+        <v>0.07065969705581665</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.06591322273015976</v>
+        <v>0.01536032371222973</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1914008259773254</v>
+        <v>0.1855512261390686</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.05493085086345673</v>
+        <v>0.03618272021412849</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0109136626124382</v>
+        <v>0.02999534271657467</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.07953828573226929</v>
+        <v>0.02735141478478909</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.6489400267601013</v>
+        <v>0.4935666620731354</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.08130860328674316</v>
+        <v>0.1343550384044647</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1412133574485779</v>
+        <v>0.02471931278705597</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.3223598599433899</v>
+        <v>0.001865439116954803</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.5394724607467651</v>
+        <v>0.2595022022724152</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1393841207027435</v>
+        <v>0.09230637550354004</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.2158317267894745</v>
+        <v>0.08178213983774185</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.07640579342842102</v>
+        <v>0.02857012301683426</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.006324121728539467</v>
+        <v>0.00412351917475462</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.3541605174541473</v>
+        <v>0.256463348865509</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.07025846838951111</v>
+        <v>0.007134913466870785</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1484997570514679</v>
+        <v>0.04258060455322266</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.006833804771304131</v>
+        <v>0.03402817994356155</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.2082442343235016</v>
+        <v>0.1104532778263092</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.02913582324981689</v>
+        <v>0.05900798365473747</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.03901132568717003</v>
+        <v>0.01387977413833141</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.007424009963870049</v>
+        <v>0.008629639632999897</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.4250453114509583</v>
+        <v>0.2815709412097931</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.5528534054756165</v>
+        <v>0.3153178095817566</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.05596272647380829</v>
+        <v>0.1942168176174164</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0357157327234745</v>
+        <v>0.1474358886480331</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.07953032851219177</v>
+        <v>0.03897995874285698</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.0816119983792305</v>
+        <v>0.1594516336917877</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.117712065577507</v>
+        <v>0.005184594541788101</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1821007430553436</v>
+        <v>0.04397872090339661</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.4050796329975128</v>
+        <v>0.009684808552265167</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.007653762586414814</v>
+        <v>0.04856318607926369</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2974154353141785</v>
+        <v>0.2462160885334015</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.09311534464359283</v>
+        <v>0.02618326060473919</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2233976423740387</v>
+        <v>0.07116537541151047</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.02268528006970882</v>
+        <v>0.05653615295886993</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2314110994338989</v>
+        <v>0.1166686415672302</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.09488965570926666</v>
+        <v>0.01598070189356804</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.111930713057518</v>
+        <v>0.01132950186729431</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.02705643139779568</v>
+        <v>0.02207822166383266</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2345219403505325</v>
+        <v>0.1911260336637497</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1791856288909912</v>
+        <v>0.07895545661449432</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0783623680472374</v>
+        <v>0.04963039606809616</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.04114949703216553</v>
+        <v>0.03900754079222679</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.3758526146411896</v>
+        <v>0.2235512733459473</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1887859106063843</v>
+        <v>0.03854909539222717</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.1285765469074249</v>
+        <v>0.08134402334690094</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1699250787496567</v>
+        <v>0.008008481934666634</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.1022553443908691</v>
+        <v>0.1536014080047607</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.09823788702487946</v>
+        <v>0.1679434776306152</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.05346996337175369</v>
+        <v>0.1437002122402191</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.2164042294025421</v>
+        <v>0.009736797772347927</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1088670194149017</v>
+        <v>0.05504411831498146</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.08047182857990265</v>
+        <v>0.01376217510551214</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.04331200569868088</v>
+        <v>0.03667541220784187</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1745522618293762</v>
+        <v>0.01941850036382675</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2184223830699921</v>
+        <v>0.146401584148407</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.1231001913547516</v>
+        <v>0.01021217834204435</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1900409609079361</v>
+        <v>0.05451944842934608</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2769032418727875</v>
+        <v>0.1211098209023476</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2403308004140854</v>
+        <v>0.06145740672945976</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.1154541671276093</v>
+        <v>0.06567125022411346</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1947430372238159</v>
+        <v>0.06671702861785889</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.09513277560472488</v>
+        <v>0.03769869357347488</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.09271187335252762</v>
+        <v>0.05477529019117355</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.1674489080905914</v>
+        <v>2.486613811925054e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.01156231015920639</v>
+        <v>0.1681613624095917</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.1085101068019867</v>
+        <v>0.05251470953226089</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2905190587043762</v>
+        <v>0.05650780722498894</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.04743346199393272</v>
+        <v>0.02704480662941933</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0634341835975647</v>
+        <v>0.005663422867655754</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1284323632717133</v>
+        <v>0.1074528247117996</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.08215585350990295</v>
+        <v>0.0255573745816946</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.0091090127825737</v>
+        <v>0.005559517070651054</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.1033469066023827</v>
+        <v>0.03807798400521278</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.2354376465082169</v>
+        <v>0.02378303371369839</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.1859568357467651</v>
+        <v>0.09019161760807037</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.124602846801281</v>
+        <v>0.1296258121728897</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1782185733318329</v>
+        <v>0.090016208589077</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.0002958138938993216</v>
+        <v>0.0798637717962265</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01358962059020996</v>
+        <v>0.09249415993690491</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.1527622938156128</v>
+        <v>0.05488181114196777</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.1560676693916321</v>
+        <v>0.02795642614364624</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.03929977118968964</v>
+        <v>0.07878927886486053</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.008394859731197357</v>
+        <v>0.009324939921498299</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02701885811984539</v>
+        <v>0.02951228991150856</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.3185179829597473</v>
+        <v>0.2835532128810883</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.05197582393884659</v>
+        <v>0.006609654985368252</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.1125365942716599</v>
+        <v>0.05625244602560997</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.05162462964653969</v>
+        <v>0.05583452433347702</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2400005757808685</v>
+        <v>0.1129658296704292</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.0008117444813251495</v>
+        <v>0.07643285393714905</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.0372311919927597</v>
+        <v>0.009050972759723663</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.04286254942417145</v>
+        <v>0.02969708666205406</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.0749625638127327</v>
+        <v>0.06717729568481445</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1341122388839722</v>
+        <v>0.1626139134168625</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.3537243604660034</v>
+        <v>0.06252144277095795</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.3028016686439514</v>
+        <v>0.1502356976270676</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.2205495536327362</v>
+        <v>0.06210841983556747</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.3426446914672852</v>
+        <v>0.1344036757946014</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.2607020735740662</v>
+        <v>0.05771644040942192</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.03546122461557388</v>
+        <v>0.246291384100914</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.07360062748193741</v>
+        <v>0.1209618672728539</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06933387368917465</v>
+        <v>0.2909911572933197</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.5677131414413452</v>
+        <v>0.2553200721740723</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.25572669506073</v>
+        <v>0.09058844298124313</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.5130107998847961</v>
+        <v>0.3170524835586548</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04182445630431175</v>
+        <v>0.1725694984197617</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.3841651976108551</v>
+        <v>0.1031722351908684</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.08028659224510193</v>
+        <v>0.01704074814915657</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.05595435202121735</v>
+        <v>0.04802897199988365</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.07030685245990753</v>
+        <v>0.00258190929889679</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.3221674561500549</v>
+        <v>0.004905526526272297</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.1506612598896027</v>
+        <v>0.03257068246603012</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1210943311452866</v>
+        <v>0.04831419140100479</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.1247126758098602</v>
+        <v>0.0704524964094162</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.6449909210205078</v>
+        <v>0.05673493817448616</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3274495303630829</v>
+        <v>0.01068722084164619</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3742668628692627</v>
+        <v>0.1536653935909271</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.06651467829942703</v>
+        <v>0.005512747913599014</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1220041364431381</v>
+        <v>0.07802174985408783</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05820314213633537</v>
+        <v>0.5574753284454346</v>
       </c>
       <c r="B4" t="n">
-        <v>0.427114874124527</v>
+        <v>1.109179258346558</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03133897855877876</v>
+        <v>0.07830314338207245</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2633202373981476</v>
+        <v>0.1293262839317322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0621027946472168</v>
+        <v>0.1219776272773743</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3037694096565247</v>
+        <v>0.4306618571281433</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01634705252945423</v>
+        <v>0.01069460064172745</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09595222771167755</v>
+        <v>0.1657743155956268</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04628715664148331</v>
+        <v>0.08189353346824646</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1347532868385315</v>
+        <v>0.4051630795001984</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3272359669208527</v>
+        <v>1.29026985168457</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008197493851184845</v>
+        <v>0.2607821226119995</v>
       </c>
       <c r="M4" t="n">
-        <v>0.234705850481987</v>
+        <v>0.5745759606361389</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04895946756005287</v>
+        <v>0.1501200199127197</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3471284508705139</v>
+        <v>0.4010472297668457</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002648457884788513</v>
+        <v>0.09679848700761795</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007580909878015518</v>
+        <v>0.1250111758708954</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0532505214214325</v>
+        <v>0.03059650957584381</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03960704430937767</v>
+        <v>0.07829354703426361</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06112472712993622</v>
+        <v>0.288441926240921</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03545567020773888</v>
+        <v>0.03868201747536659</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05692069232463837</v>
+        <v>0.1976126432418823</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0279327966272831</v>
+        <v>0.1654456257820129</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02557237073779106</v>
+        <v>0.0381445549428463</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05690335854887962</v>
+        <v>0.07053110748529434</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03842366114258766</v>
+        <v>0.2360555380582809</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05055372789502144</v>
+        <v>0.008883319795131683</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0002070460468530655</v>
+        <v>0.002672323957085609</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04465112090110779</v>
+        <v>0.1701003909111023</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.02440403588116169</v>
+        <v>0.006680998951196671</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0005625202320516109</v>
+        <v>0.3599786758422852</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01799420639872551</v>
+        <v>0.4686067402362823</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.004050122573971748</v>
+        <v>0.2412310242652893</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.02441317215561867</v>
+        <v>0.06052560359239578</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03598549962043762</v>
+        <v>0.3678901493549347</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.037112046033144</v>
+        <v>0.1202700436115265</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03774325549602509</v>
+        <v>0.002547822892665863</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.07314363867044449</v>
+        <v>0.2406878620386124</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.02266141958534718</v>
+        <v>0.08473408967256546</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0004321467131376266</v>
+        <v>0.009389776736497879</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.02318612858653069</v>
+        <v>0.2245578467845917</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.05439485982060432</v>
+        <v>0.2148811817169189</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.009026544168591499</v>
+        <v>0.118064858019352</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.03928947076201439</v>
+        <v>0.378314733505249</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.06106070056557655</v>
+        <v>0.02219803631305695</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.03184117376804352</v>
+        <v>0.1962539851665497</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.272275298833847</v>
+        <v>1.139817237854004</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.02178372070193291</v>
+        <v>0.1297526508569717</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04523279517889023</v>
+        <v>0.05962129682302475</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.04085651412606239</v>
+        <v>0.250834047794342</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.149662971496582</v>
+        <v>0.4377528131008148</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02178179658949375</v>
+        <v>0.02626417391002178</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.05276514962315559</v>
+        <v>0.02307255379855633</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0865166112780571</v>
+        <v>0.01636584848165512</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.07230944186449051</v>
+        <v>0.1447689682245255</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.07603241503238678</v>
+        <v>0.01342040300369263</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1234653815627098</v>
+        <v>0.07896358519792557</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.07960883527994156</v>
+        <v>0.1655979156494141</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1045583337545395</v>
+        <v>0.2740149796009064</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.08581310510635376</v>
+        <v>0.1539599895477295</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.01260006800293922</v>
+        <v>0.151961624622345</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.06867058575153351</v>
+        <v>0.09031261503696442</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.04049591720104218</v>
+        <v>0.06102675572037697</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.01394042931497097</v>
+        <v>0.1221541836857796</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05365542322397232</v>
+        <v>0.08459648489952087</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.05508981272578239</v>
+        <v>0.01561068557202816</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.05432036146521568</v>
+        <v>0.0715285986661911</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02127132005989552</v>
+        <v>0.1100711897015572</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001950934529304504</v>
+        <v>0.05832752212882042</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.02064716070890427</v>
+        <v>0.1517426371574402</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.02723811753094196</v>
+        <v>0.04932954162359238</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.01280481275171041</v>
+        <v>0.008705552667379379</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.03160160407423973</v>
+        <v>0.0752611979842186</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1363173574209213</v>
+        <v>0.8575886487960815</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.06409593671560287</v>
+        <v>0.06307453662157059</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.08944448828697205</v>
+        <v>0.1268031299114227</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0501336045563221</v>
+        <v>0.1198671162128448</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.05731690302491188</v>
+        <v>0.2841894328594208</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.02934453636407852</v>
+        <v>0.1563750505447388</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.02981076948344707</v>
+        <v>0.1482585519552231</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.06873860210180283</v>
+        <v>0.03520495072007179</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.008654293604195118</v>
+        <v>0.1038911938667297</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0661480501294136</v>
+        <v>0.339138388633728</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.06202508509159088</v>
+        <v>0.01626797579228878</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0445738285779953</v>
+        <v>0.1080919578671455</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.02250472828745842</v>
+        <v>0.01437421143054962</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.05814843624830246</v>
+        <v>0.1611790210008621</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.01928051561117172</v>
+        <v>0.07393385469913483</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.01912199705839157</v>
+        <v>0.007042724639177322</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.03711248189210892</v>
+        <v>0.04791541770100594</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.04764892905950546</v>
+        <v>0.3027878999710083</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.007708967197686434</v>
+        <v>0.7742046713829041</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.01992723345756531</v>
+        <v>0.1122018322348595</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001715710386633873</v>
+        <v>0.2626356780529022</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0239369198679924</v>
+        <v>0.3683057427406311</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003417892381548882</v>
+        <v>0.459111362695694</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.05558910220861435</v>
+        <v>0.02679372578859329</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.06198750436306</v>
+        <v>0.02314552292227745</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.02745396830141544</v>
+        <v>0.065106600522995</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.001586017664521933</v>
+        <v>0.02986055612564087</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.05905310437083244</v>
+        <v>0.3264468610286713</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.05781860277056694</v>
+        <v>0.009527551010251045</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.06416304409503937</v>
+        <v>0.08485889434814453</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01552697643637657</v>
+        <v>0.07562894374132156</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0680822879076004</v>
+        <v>0.1314748972654343</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01801540702581406</v>
+        <v>0.01623101904988289</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.04350678622722626</v>
+        <v>0.02932830899953842</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.01924116164445877</v>
+        <v>0.09171512722969055</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.03382318466901779</v>
+        <v>0.3822558522224426</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.04739577695727348</v>
+        <v>0.106058806180954</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.01762278005480766</v>
+        <v>0.05389152094721794</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1418601274490356</v>
+        <v>0.1171673312783241</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0103995930403471</v>
+        <v>0.2586706578731537</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.06254030019044876</v>
+        <v>0.1123310104012489</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.02669833041727543</v>
+        <v>0.1952080428600311</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.03486035019159317</v>
+        <v>0.003999797627329826</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.004771032370626926</v>
+        <v>0.2307948917150497</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.005835811607539654</v>
+        <v>0.04510969668626785</v>
       </c>
       <c r="DO4" t="n">
-        <v>4.237191751599312e-05</v>
+        <v>0.07272568345069885</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.03067848458886147</v>
+        <v>0.09875056892633438</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0475146695971489</v>
+        <v>0.1895345896482468</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01867482624948025</v>
+        <v>0.03311295062303543</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01909280382096767</v>
+        <v>0.006028838455677032</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.05588211864233017</v>
+        <v>0.02956992387771606</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001527171581983566</v>
+        <v>0.2353241294622421</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.08440347015857697</v>
+        <v>0.002165701240301132</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0191228836774826</v>
+        <v>0.1292677968740463</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.03129398077726364</v>
+        <v>0.2035964578390121</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.08351793140172958</v>
+        <v>0.1927222907543182</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.005903306882828474</v>
+        <v>0.01722101867198944</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.01009432226419449</v>
+        <v>0.1296784281730652</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.03553570434451103</v>
+        <v>0.1128856539726257</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.01165065169334412</v>
+        <v>0.01383663341403008</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.04473041370511055</v>
+        <v>0.04362596943974495</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.03142294660210609</v>
+        <v>0.2529944777488708</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.02887651510536671</v>
+        <v>0.08852022141218185</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.04863578081130981</v>
+        <v>0.04955555126070976</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.04543042927980423</v>
+        <v>0.01213871873915195</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.007376119494438171</v>
+        <v>0.02198940701782703</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.004759647883474827</v>
+        <v>0.1868817210197449</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.07944966107606888</v>
+        <v>0.02935424819588661</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.01857121661305428</v>
+        <v>0.01681127399206161</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.002579864580184221</v>
+        <v>0.0773904100060463</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.01104890555143356</v>
+        <v>0.0464395210146904</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0004507210105657578</v>
+        <v>0.01497401669621468</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.02628185227513313</v>
+        <v>0.1586714237928391</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.06223439425230026</v>
+        <v>0.04974984750151634</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.03330141678452492</v>
+        <v>0.1065640598535538</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.02107765898108482</v>
+        <v>0.3277325630187988</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04696949943900108</v>
+        <v>0.09581020474433899</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.03975817561149597</v>
+        <v>0.02394960075616837</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.08019483089447021</v>
+        <v>0.1042222529649734</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.005158334970474243</v>
+        <v>0.06835943460464478</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.004233862273395061</v>
+        <v>0.07340977340936661</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.05664365738630295</v>
+        <v>0.3787517845630646</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.04810936748981476</v>
+        <v>0.01899519935250282</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.05849950015544891</v>
+        <v>0.1016118973493576</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.02409357950091362</v>
+        <v>0.08817653357982635</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.05473070591688156</v>
+        <v>0.1502058804035187</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.03216205164790154</v>
+        <v>0.09588722139596939</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.02413243800401688</v>
+        <v>0.0092631746083498</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.03487608954310417</v>
+        <v>0.09636723250150681</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.00972035713493824</v>
+        <v>0.0178288072347641</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.03278931230306625</v>
+        <v>0.2943629324436188</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.06004271656274796</v>
+        <v>0.01870729401707649</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.05406949669122696</v>
+        <v>0.252820611000061</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.009165075607597828</v>
+        <v>0.1877405494451523</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0479234978556633</v>
+        <v>0.1304734349250793</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.03543504327535629</v>
+        <v>0.1223405376076698</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.04141245782375336</v>
+        <v>0.3511893749237061</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0285356342792511</v>
+        <v>0.01601526513695717</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.01371928863227367</v>
+        <v>0.4217522740364075</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.08992103487253189</v>
+        <v>0.7452857494354248</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.04224938154220581</v>
+        <v>0.1741393357515335</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.09688316285610199</v>
+        <v>0.4489535689353943</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0724637359380722</v>
+        <v>0.1003909856081009</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.003599477000534534</v>
+        <v>0.2351135313510895</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.02626558393239975</v>
+        <v>0.1695748120546341</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.01732093468308449</v>
+        <v>0.05000638589262962</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.006335332058370113</v>
+        <v>0.1176447793841362</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.08346714824438095</v>
+        <v>0.1554223299026489</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.01610144972801208</v>
+        <v>0.1078816205263138</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.02075017429888248</v>
+        <v>0.06883079558610916</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.006805709097534418</v>
+        <v>0.3521277904510498</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.04067938029766083</v>
+        <v>0.1281957626342773</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.03074569627642632</v>
+        <v>0.1676123440265656</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.2242997139692307</v>
+        <v>0.1120707988739014</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.01249695383012295</v>
+        <v>0.02992241829633713</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.04457202181220055</v>
+        <v>0.1366100907325745</v>
       </c>
     </row>
     <row r="5">
@@ -3275,2278 +3275,2278 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.01554986089468002</v>
+        <v>2.251907426398247e-05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07014036923646927</v>
+        <v>0.0001453703735023737</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00990816205739975</v>
+        <v>9.763858543010429e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02057818695902824</v>
+        <v>4.815342981601134e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04239463806152344</v>
+        <v>4.238596739014611e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002097753109410405</v>
+        <v>4.419248216436245e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01067756116390228</v>
+        <v>4.499032002058811e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001380008179694414</v>
+        <v>2.802296330628451e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001712454832158983</v>
+        <v>3.111548721790314e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00850962195545435</v>
+        <v>1.219607111124787e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05022390931844711</v>
+        <v>0.0001791459653759375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006871121935546398</v>
+        <v>4.261820322426502e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02548253163695335</v>
+        <v>0.0001020718409563415</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04197346791625023</v>
+        <v>0.000112703513877932</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0110950693488121</v>
+        <v>5.053013956057839e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001232702750712633</v>
+        <v>2.370816946495324e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02883544191718102</v>
+        <v>3.226052649552003e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003123383270576596</v>
+        <v>2.650531314429827e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00148590502794832</v>
+        <v>1.114157839765539e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02482464909553528</v>
+        <v>5.159576176083647e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>2.814098843373358e-05</v>
+        <v>1.465209334128303e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002084101084619761</v>
+        <v>3.280886812717654e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009272863157093525</v>
+        <v>4.024996087537147e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01045862771570683</v>
+        <v>7.862802704039495e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01056931260973215</v>
+        <v>1.180291292257607e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001095861662179232</v>
+        <v>1.659036570345052e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006463431287556887</v>
+        <v>1.722129309200682e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008662862703204155</v>
+        <v>1.340801190963248e-06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01861467026174068</v>
+        <v>8.486075785185676e-06</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.006873979233205318</v>
+        <v>1.559671909490135e-05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.009312724694609642</v>
+        <v>6.534085696330294e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01231355778872967</v>
+        <v>8.451545727439225e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001865212805569172</v>
+        <v>5.783221240562852e-06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.01632852852344513</v>
+        <v>3.349513463035692e-06</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.00452168844640255</v>
+        <v>4.58372087450698e-05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.001410966156981885</v>
+        <v>4.608927611116087e-06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0117957815527916</v>
+        <v>3.592417442632723e-06</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01724098064005375</v>
+        <v>4.538830035016872e-05</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.004012210294604301</v>
+        <v>3.165808948324411e-07</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.005322746932506561</v>
+        <v>6.313201993179973e-06</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.003512540832161903</v>
+        <v>2.217844667029567e-06</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.003411879297345877</v>
+        <v>7.898962394392584e-06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.003405584255233407</v>
+        <v>1.92197894648416e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.002190755913034081</v>
+        <v>1.997319486690685e-05</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.005157936364412308</v>
+        <v>1.058393354469445e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01791307888925076</v>
+        <v>3.884133548126556e-08</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.07147007435560226</v>
+        <v>0.0001910550781758502</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.005724911112338305</v>
+        <v>6.960315658943728e-06</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.003587245708331466</v>
+        <v>5.727473762817681e-06</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.005477622617036104</v>
+        <v>0.0001097502608899958</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.002690784633159637</v>
+        <v>1.583048288011923e-05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001112047233618796</v>
+        <v>5.755948222940788e-06</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0114130349829793</v>
+        <v>1.83839238161454e-05</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.206547888927162e-05</v>
+        <v>1.666718708293047e-05</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.00731323566287756</v>
+        <v>2.989083623106126e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.009170481003820896</v>
+        <v>4.208840618957765e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01075813453644514</v>
+        <v>1.256233190360945e-05</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.00681858416646719</v>
+        <v>3.903676770278253e-05</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.02529018931090832</v>
+        <v>4.595869540935382e-05</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01164405886083841</v>
+        <v>1.065482047124533e-05</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.005726491566747427</v>
+        <v>1.986172537726816e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.02062829956412315</v>
+        <v>2.549268901930191e-05</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.004002900328487158</v>
+        <v>1.275307295145467e-05</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.009336965158581734</v>
+        <v>2.129107815562747e-05</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02243887446820736</v>
+        <v>2.44660895987181e-05</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.003151390934363008</v>
+        <v>3.478400685708039e-06</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02280834503471851</v>
+        <v>3.499414560792502e-06</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02214523404836655</v>
+        <v>2.421798853902146e-05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01527787279337645</v>
+        <v>2.249263161502313e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.000123028177767992</v>
+        <v>4.695173629443161e-05</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.007544208317995071</v>
+        <v>1.155647441919427e-05</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.00286469329148531</v>
+        <v>1.742898348311428e-06</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.00950933713465929</v>
+        <v>3.708559961523861e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.04013717547059059</v>
+        <v>0.0001285487232962623</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.01229055784642696</v>
+        <v>5.614007022813894e-06</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.002165388781577349</v>
+        <v>3.9200243918458e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.002201937139034271</v>
+        <v>4.325605186750181e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.008176990784704685</v>
+        <v>1.517185773991514e-05</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0166260227560997</v>
+        <v>2.977258918690495e-05</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.007690258324146271</v>
+        <v>8.127902219712269e-06</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.003632539650425315</v>
+        <v>3.118239419563906e-06</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0009689830476418138</v>
+        <v>6.185530310176546e-07</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0124470517039299</v>
+        <v>4.281608926248737e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0001853102876339108</v>
+        <v>7.935266694403253e-06</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.009941259399056435</v>
+        <v>2.682226295291912e-06</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.004262890666723251</v>
+        <v>2.167522325180471e-05</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.00498903077095747</v>
+        <v>1.495665856054984e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.001050698570907116</v>
+        <v>4.041323336423375e-06</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0001968028082046658</v>
+        <v>2.781481953206821e-06</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.004704682622104883</v>
+        <v>3.308987515993067e-06</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.02770276740193367</v>
+        <v>3.781196210184135e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.02489689365029335</v>
+        <v>8.357129263458773e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0006756768561899662</v>
+        <v>1.560186319693457e-05</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.008321085013449192</v>
+        <v>5.030242027714849e-05</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0270823035389185</v>
+        <v>0.0001130914024543017</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.003042312804609537</v>
+        <v>9.348143066745251e-06</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.002446394180878997</v>
+        <v>1.701785004115663e-05</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.005624583456665277</v>
+        <v>2.103822407661937e-05</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0008474006317555904</v>
+        <v>8.919411811803002e-06</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0004391064867377281</v>
+        <v>1.251545563718537e-05</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.009305836632847786</v>
+        <v>4.081064253114164e-05</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.002692129462957382</v>
+        <v>9.289801710110623e-06</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01411662809550762</v>
+        <v>5.848695764143486e-06</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002311107935383916</v>
+        <v>1.655589949223213e-05</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006282894872128963</v>
+        <v>1.246943611477036e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0004940289072692394</v>
+        <v>1.387313659506617e-06</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.003056678222492337</v>
+        <v>1.00155148174963e-05</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.002491939347237349</v>
+        <v>4.388642082631122e-06</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.02101856470108032</v>
+        <v>4.298018393456005e-05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.03990837559103966</v>
+        <v>1.185162909678183e-05</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.003059873823076487</v>
+        <v>1.162770786322653e-07</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.03410201892256737</v>
+        <v>4.541692760540172e-06</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01159583125263453</v>
+        <v>2.06343102036044e-05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.002051133429631591</v>
+        <v>2.091446003760211e-05</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.04074326902627945</v>
+        <v>6.286757525231224e-06</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.01250117458403111</v>
+        <v>7.708249540883116e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.004076436161994934</v>
+        <v>6.789487088099122e-05</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01374116912484169</v>
+        <v>2.007056536967866e-06</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01309563964605331</v>
+        <v>2.398384822299704e-05</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.003933674190193415</v>
+        <v>7.490646567021031e-06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.001396221457980573</v>
+        <v>2.246590884169564e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01383760198950768</v>
+        <v>2.246463918709196e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.008790909312665462</v>
+        <v>2.77786202786956e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.003991243429481983</v>
+        <v>1.816729673009831e-05</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.004748451057821512</v>
+        <v>1.659447480051313e-05</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.006044522393494844</v>
+        <v>3.07026130030863e-06</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.003851134330034256</v>
+        <v>2.079445584968198e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.003935130778700113</v>
+        <v>4.342978718341328e-05</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.008078459650278091</v>
+        <v>6.313996436801972e-06</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.01526822056621313</v>
+        <v>3.907749942300143e-06</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01313319336622953</v>
+        <v>6.265655974857509e-05</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.00144685769919306</v>
+        <v>2.621085513965227e-06</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.009284209460020065</v>
+        <v>1.561285898787901e-05</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0003104851930402219</v>
+        <v>9.471297744312324e-06</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.003129132557660341</v>
+        <v>7.402418304991443e-06</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.008979173377156258</v>
+        <v>7.827316949260421e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>2.007824514294043e-05</v>
+        <v>8.170742148649879e-06</v>
       </c>
       <c r="EH6" t="n">
-        <v>6.68869906803593e-05</v>
+        <v>5.771150426880922e-06</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.02280188351869583</v>
+        <v>1.354193045699503e-06</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01304988097399473</v>
+        <v>1.131525823439006e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.004745736718177795</v>
+        <v>1.240904748556204e-05</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.004542926326394081</v>
+        <v>9.136303560808301e-06</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.002107461215928197</v>
+        <v>3.267266947659664e-06</v>
       </c>
       <c r="EN6" t="n">
-        <v>3.53704672306776e-05</v>
+        <v>2.345723032703972e-06</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.009966103360056877</v>
+        <v>1.132233410316985e-05</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.003866207785904408</v>
+        <v>9.781830158317462e-06</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01256202720105648</v>
+        <v>2.775795564957662e-06</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.01191132795065641</v>
+        <v>5.032492481404915e-06</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.001274274429306388</v>
+        <v>2.772267544060014e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.008907058276236057</v>
+        <v>9.991062142944429e-06</v>
       </c>
       <c r="EU6" t="n">
-        <v>2.395396586507559e-05</v>
+        <v>1.412388428434497e-06</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.006601540837436914</v>
+        <v>1.189776048704516e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.004005837254226208</v>
+        <v>1.565841921546962e-05</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0007331091910600662</v>
+        <v>3.842874320980627e-06</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.007187142968177795</v>
+        <v>4.622028427547775e-05</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.001204623724333942</v>
+        <v>5.630597570416285e-06</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01120935752987862</v>
+        <v>6.128119821369182e-06</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001111085526645184</v>
+        <v>1.235505442309659e-05</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.005561096593737602</v>
+        <v>1.162059470516397e-05</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.002673451323062181</v>
+        <v>4.84272959511145e-06</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.001448634313419461</v>
+        <v>6.878368822071934e-06</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.003679746063426137</v>
+        <v>1.192873423860874e-05</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.01061735395342112</v>
+        <v>2.050078728643712e-05</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01673528552055359</v>
+        <v>1.401533336320426e-05</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.009411588311195374</v>
+        <v>2.758849177553202e-06</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.003606434678658843</v>
+        <v>3.103678682236932e-05</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.005480068270117044</v>
+        <v>3.712618854478933e-05</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.003711296012625098</v>
+        <v>9.117447916651145e-06</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.002236240776255727</v>
+        <v>1.934083957166877e-05</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.001674933591857553</v>
+        <v>3.213651507394388e-05</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.001081352005712688</v>
+        <v>3.253828253946267e-06</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.005856226198375225</v>
+        <v>1.779743251972832e-05</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.001486103748902678</v>
+        <v>6.823094736319035e-05</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.007067886646836996</v>
+        <v>2.493509600753896e-05</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02562012895941734</v>
+        <v>3.299889795016497e-05</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01294733304530382</v>
+        <v>8.797578630037606e-05</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.004354092758148909</v>
+        <v>4.448775143828243e-06</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0009708848083391786</v>
+        <v>9.163028153125197e-06</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.02096831798553467</v>
+        <v>4.259821253072005e-06</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.002535826992243528</v>
+        <v>1.425381924491376e-05</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.005712715908885002</v>
+        <v>1.789177622413263e-05</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01935379952192307</v>
+        <v>2.685356776055414e-05</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0120299244299531</v>
+        <v>2.466829027980566e-05</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01084455661475658</v>
+        <v>2.148956991732121e-05</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.004121070727705956</v>
+        <v>2.993250745930709e-05</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0124049223959446</v>
+        <v>4.838080258195987e-06</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.02001896873116493</v>
+        <v>1.789415182429366e-05</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.01758640632033348</v>
+        <v>1.301263910136186e-05</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0006765954894945025</v>
+        <v>3.43402780345059e-06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.03218394890427589</v>
+        <v>0.02323138527572155</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2123985588550568</v>
+        <v>0.03106526657938957</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001970803714357316</v>
+        <v>0.007582566235214472</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05954695492982864</v>
+        <v>0.0009203427471220493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02524762973189354</v>
+        <v>0.008050419390201569</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03512627258896828</v>
+        <v>0.0008134954841807485</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01569333486258984</v>
+        <v>0.002421096665784717</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006874158512800932</v>
+        <v>0.003787415567785501</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03799623996019363</v>
+        <v>0.008267098106443882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04798310995101929</v>
+        <v>0.02296377904713154</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1551417857408524</v>
+        <v>0.04188401252031326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000998667674139142</v>
+        <v>0.00830546859651804</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04970483481884003</v>
+        <v>0.005047674290835857</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05197658762335777</v>
+        <v>0.01400737836956978</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0496181957423687</v>
+        <v>0.008458489552140236</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02153880521655083</v>
+        <v>0.00212637335062027</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01459823828190565</v>
+        <v>0.005610655527561903</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04297695308923721</v>
+        <v>0.01457512285560369</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008007552474737167</v>
+        <v>0.00134125561453402</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04505261033773422</v>
+        <v>0.002084814244881272</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003305527381598949</v>
+        <v>0.001017354195937514</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0317438617348671</v>
+        <v>0.003452051198109984</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0118562038987875</v>
+        <v>0.001585369696840644</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03326409682631493</v>
+        <v>0.003316709771752357</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01038662437349558</v>
+        <v>0.0001823985367082059</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02983665093779564</v>
+        <v>0.007117354311048985</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01563754491508007</v>
+        <v>0.006153897847980261</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005570209585130215</v>
+        <v>0.002816240303218365</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02365129627287388</v>
+        <v>0.003321904689073563</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.008226718753576279</v>
+        <v>0.002823949558660388</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.009622259996831417</v>
+        <v>0.005612788256257772</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03183324635028839</v>
+        <v>0.007341057527810335</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04511312395334244</v>
+        <v>0.0006677817436866462</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01111134327948093</v>
+        <v>0.002583344001322985</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.005103253293782473</v>
+        <v>0.003301578108221292</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01390464045107365</v>
+        <v>0.001298816874623299</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02250746451318264</v>
+        <v>0.005155757535248995</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0423847995698452</v>
+        <v>0.009551210328936577</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.005781557876616716</v>
+        <v>0.004804655443876982</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0195271410048008</v>
+        <v>0.005566958338022232</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.00570294726639986</v>
+        <v>0.00153848621994257</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.02020914852619171</v>
+        <v>0.0007018429460003972</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01106815133243799</v>
+        <v>0.003922357689589262</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.008861131966114044</v>
+        <v>0.004774117842316628</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0199778713285923</v>
+        <v>0.0006646037800237536</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.004278106149286032</v>
+        <v>0.00924577284604311</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1301725804805756</v>
+        <v>0.02477611042559147</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0126482043415308</v>
+        <v>0.003785140113905072</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0162052046507597</v>
+        <v>0.003789097303524613</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.01565140672028065</v>
+        <v>0.004836753942072392</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.02215870469808578</v>
+        <v>0.004839300643652678</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.009280575439333916</v>
+        <v>9.378010872751474e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.01163647882640362</v>
+        <v>0.0001881578064057976</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.004251575563102961</v>
+        <v>0.001327602891251445</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.004964271560311317</v>
+        <v>0.005291454493999481</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02988169528543949</v>
+        <v>8.505117148160934e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01530836336314678</v>
+        <v>0.007553842384368181</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.00561278872191906</v>
+        <v>0.0003223868552595377</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.04413518309593201</v>
+        <v>0.007040021475404501</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006751604378223419</v>
+        <v>0.007480467204004526</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.02079491317272186</v>
+        <v>0.001501751248724759</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.01403764449059963</v>
+        <v>0.002470530569553375</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.03011903539299965</v>
+        <v>0.005897273309528828</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.005082030780613422</v>
+        <v>0.003068313235417008</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.009723127819597721</v>
+        <v>0.004047286696732044</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0007646736921742558</v>
+        <v>0.001185010885819793</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01137683913111687</v>
+        <v>0.0002086812164634466</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02862579561769962</v>
+        <v>0.003717484883964062</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02628187462687492</v>
+        <v>0.0003823278821073472</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.004092734772711992</v>
+        <v>0.007748704869300127</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01555137615650892</v>
+        <v>0.0007860062178224325</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02620325796306133</v>
+        <v>0.001145778805948794</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.008584808558225632</v>
+        <v>0.002582892775535583</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09379476308822632</v>
+        <v>0.02118542790412903</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01747508719563484</v>
+        <v>0.0009635635651648045</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.03247115015983582</v>
+        <v>0.003376293927431107</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0002523130387999117</v>
+        <v>0.0006189525010995567</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.005798126105219126</v>
+        <v>0.0003257656644564122</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.005874317139387131</v>
+        <v>0.004649373702704906</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01662790030241013</v>
+        <v>0.001401938730850816</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0148118007928133</v>
+        <v>0.006247374229133129</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.006990291178226471</v>
+        <v>0.006874875631183386</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.03027556091547012</v>
+        <v>0.01066372636705637</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.009601371362805367</v>
+        <v>0.0008536549285054207</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.007003752049058676</v>
+        <v>0.0001353393890894949</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.003352616913616657</v>
+        <v>0.0007128308061510324</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.005071286112070084</v>
+        <v>0.003150101052597165</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.004557847045361996</v>
+        <v>0.001790367416106164</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.007511753588914871</v>
+        <v>0.001142250373959541</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.002126110950484872</v>
+        <v>0.001592735992744565</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.03517862781882286</v>
+        <v>0.001565249636769295</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0001045982935465872</v>
+        <v>0.0215699914842844</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0005648810183629394</v>
+        <v>0.0006125608924776316</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01469586230814457</v>
+        <v>0.004502804018557072</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.03851167485117912</v>
+        <v>0.0009307030122727156</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.009540685452520847</v>
+        <v>0.008029846474528313</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.01921222545206547</v>
+        <v>0.002435321919620037</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.01412814203649759</v>
+        <v>0.00649631442502141</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.01987939327955246</v>
+        <v>0.003349989419803023</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.002924415282905102</v>
+        <v>0.006243014242500067</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.03093443065881729</v>
+        <v>0.01058236043900251</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.01211680565029383</v>
+        <v>0.0003793060313910246</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.01166554074734449</v>
+        <v>0.0009819632396101952</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.006839251145720482</v>
+        <v>0.001986000686883926</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01438329461961985</v>
+        <v>0.002393025206401944</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.007949544116854668</v>
+        <v>0.001061646384187043</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.008233269676566124</v>
+        <v>6.125502113718539e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0006985227228142321</v>
+        <v>0.003012808272615075</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.007390893995761871</v>
+        <v>0.006004069931805134</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.05704014748334885</v>
+        <v>0.0131382942199707</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.003267480526119471</v>
+        <v>0.001019620918668807</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.04997266083955765</v>
+        <v>0.005083571188151836</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01462891697883606</v>
+        <v>0.009837613441050053</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.05554273352026939</v>
+        <v>0.01036885846406221</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.006689688190817833</v>
+        <v>0.00137878826353699</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.003066974226385355</v>
+        <v>0.0004141924437135458</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.02291912958025932</v>
+        <v>0.007270412519574165</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.002414398826658726</v>
+        <v>0.002298285951837897</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01245310250669718</v>
+        <v>0.005460497923195362</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.008721371181309223</v>
+        <v>0.005667869932949543</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.01683135703206062</v>
+        <v>0.001561541808769107</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.02938702329993248</v>
+        <v>0.001176290214061737</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0009559514001011848</v>
+        <v>0.006411934737116098</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.003237128723412752</v>
+        <v>0.002600152511149645</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.002128139371052384</v>
+        <v>0.007320153061300516</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.02938557229936123</v>
+        <v>0.001462777727283537</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0007430021651089191</v>
+        <v>0.004600032698363066</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.02029922604560852</v>
+        <v>0.003903945442289114</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.01836094446480274</v>
+        <v>0.003959448542445898</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.005971289705485106</v>
+        <v>0.00274668144993484</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01777126267552376</v>
+        <v>0.007470551878213882</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0105474665760994</v>
+        <v>0.01064404752105474</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.002655174350365996</v>
+        <v>0.005037633236497641</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.00828669685870409</v>
+        <v>0.006633085664361715</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01359535846859217</v>
+        <v>0.006376803386956453</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.004175784531980753</v>
+        <v>0.005612928420305252</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01122288499027491</v>
+        <v>0.003924229182302952</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.005535811651498079</v>
+        <v>0.002565782517194748</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01530192419886589</v>
+        <v>0.0002109618944814429</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.004639754071831703</v>
+        <v>0.002631415845826268</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01953521743416786</v>
+        <v>0.002889480441808701</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.009476855397224426</v>
+        <v>0.001090939738787711</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001448547118343413</v>
+        <v>0.002398029202595353</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.004886786919087172</v>
+        <v>0.0002358936471864581</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.005899435840547085</v>
+        <v>0.003322256729006767</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01230136398226023</v>
+        <v>0.006307882722467184</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.01422932930290699</v>
+        <v>0.004164428450167179</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.007742155343294144</v>
+        <v>0.003981264773756266</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0003305267891846597</v>
+        <v>0.001130955992266536</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.03581495955586433</v>
+        <v>0.005263091530650854</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.01025629974901676</v>
+        <v>0.002478501293808222</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.03202563896775246</v>
+        <v>0.00159291853196919</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.004500781651586294</v>
+        <v>0.008218028582632542</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.002578237559646368</v>
+        <v>0.007028485182672739</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.03110994771122932</v>
+        <v>0.01251136511564255</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.007245442364364862</v>
+        <v>0.00148977036587894</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01311893574893475</v>
+        <v>0.0002581320004537702</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.009864292107522488</v>
+        <v>0.001875080401077867</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.01029846724122763</v>
+        <v>0.002466772217303514</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.005644898395985365</v>
+        <v>0.001292719505727291</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.00226086238399148</v>
+        <v>0.0002040871186181903</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.00441076373681426</v>
+        <v>0.003194173565134406</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.002659345045685768</v>
+        <v>0.002418313408270478</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02028720080852509</v>
+        <v>0.007780455052852631</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0142994225025177</v>
+        <v>0.005703032948076725</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01370341330766678</v>
+        <v>0.004478859715163708</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.006421097554266453</v>
+        <v>0.003203149419277906</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.00363954296335578</v>
+        <v>0.0003121391637250781</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.009028831496834755</v>
+        <v>0.004678389523178339</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.006373318377882242</v>
+        <v>0.003945471718907356</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.006435250863432884</v>
+        <v>0.008788740262389183</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01125794183462858</v>
+        <v>0.0001433438155800104</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.04275926202535629</v>
+        <v>0.003550442401319742</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.01428592298179865</v>
+        <v>0.005375315435230732</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.02745112404227257</v>
+        <v>0.003276192815974355</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001395493512973189</v>
+        <v>0.0062556485645473</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.005034955684095621</v>
+        <v>0.0010020995978266</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.02463188394904137</v>
+        <v>0.003927135374397039</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.01083041727542877</v>
+        <v>0.01221633888781071</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.01619871705770493</v>
+        <v>0.005207010544836521</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.02591996267437935</v>
+        <v>0.003787151537835598</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.002360637299716473</v>
+        <v>0.003066602628678083</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.003802358405664563</v>
+        <v>0.003538505639880896</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.009078925475478172</v>
+        <v>0.005513049196451902</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.07337432354688644</v>
+        <v>0.003034900408238173</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.03178423643112183</v>
+        <v>0.0004882480134256184</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.07348792999982834</v>
+        <v>0.0005941636627539992</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.004643549211323261</v>
+        <v>0.004664235282689333</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01076110545545816</v>
+        <v>0.01148184016346931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.009669339284300804</v>
+        <v>0.0003039823786821216</v>
       </c>
       <c r="B8" t="n">
-        <v>0.07197524607181549</v>
+        <v>0.002157620154321194</v>
       </c>
       <c r="C8" t="n">
-        <v>0.007208586670458317</v>
+        <v>0.0004427520907483995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01128796301782131</v>
+        <v>0.0007143054390326142</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01458880119025707</v>
+        <v>0.001237671356648207</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00639175483956933</v>
+        <v>0.000325841479934752</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03572084009647369</v>
+        <v>0.0008943143184296787</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003638547845184803</v>
+        <v>0.0005387059645727277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005797703634016216</v>
+        <v>0.0005327616818249226</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01504797488451004</v>
+        <v>0.0002759706112556159</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05252392962574959</v>
+        <v>0.002822389360517263</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005199961364269257</v>
+        <v>8.47060582600534e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02402882464230061</v>
+        <v>0.001205075066536665</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01588805206120014</v>
+        <v>0.00117411301471293</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009480693377554417</v>
+        <v>0.0005914032808504999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03020710870623589</v>
+        <v>0.001196901546791196</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01095870696008205</v>
+        <v>0.000615055556409061</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004982705228030682</v>
+        <v>0.0001564949925523251</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005066880024969578</v>
+        <v>0.0001320488954661414</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01756567880511284</v>
+        <v>0.0001089351062546484</v>
       </c>
       <c r="U8" t="n">
-        <v>0.006865448318421841</v>
+        <v>0.0003102290793322027</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001685940893366933</v>
+        <v>9.229508577845991e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.006230299826711416</v>
+        <v>0.0004006478702649474</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01105639711022377</v>
+        <v>0.0002938178367912769</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0009174102451652288</v>
+        <v>0.0001347926736343652</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.006776839960366488</v>
+        <v>3.086945798713714e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008380349725484848</v>
+        <v>0.0001563443220220506</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.002480211202055216</v>
+        <v>0.0001750497176544741</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01078291609883308</v>
+        <v>9.057057468453422e-07</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.00347242271527648</v>
+        <v>0.0006369815673679113</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0001871143467724323</v>
+        <v>0.0002037200465565547</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0101988110691309</v>
+        <v>0.0001407336676493287</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.007605582475662231</v>
+        <v>6.182202196214348e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.001820549834519625</v>
+        <v>0.0001438200415577739</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.002633143682032824</v>
+        <v>0.0003784611471928656</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.007268025539815426</v>
+        <v>0.0002816715277731419</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01112830732017756</v>
+        <v>8.979623817140236e-05</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01300337072461843</v>
+        <v>0.0007405400392599404</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.002689098240807652</v>
+        <v>8.637505379738286e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.006893530953675508</v>
+        <v>8.34611855680123e-05</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003425454022362828</v>
+        <v>0.0004351946990936995</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0006701464881189167</v>
+        <v>0.000252564757829532</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003569005290046334</v>
+        <v>4.615938087226823e-05</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.002421800745651126</v>
+        <v>0.0001636685337871313</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.005275605712085962</v>
+        <v>4.355404962552711e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00879957340657711</v>
+        <v>0.0002469827886670828</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.05556334927678108</v>
+        <v>0.002113317139446735</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001364546827971935</v>
+        <v>0.0004464611411094666</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01097512152045965</v>
+        <v>0.0001742503081914037</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.006995928473770618</v>
+        <v>0.0001481490908190608</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.01119549106806517</v>
+        <v>0.000429287611041218</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.01192539464682341</v>
+        <v>0.0001388275704812258</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.009154334664344788</v>
+        <v>0.0005145137547515333</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004797652829438448</v>
+        <v>0.0001849451800808311</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.006779001094400883</v>
+        <v>7.870455738157034e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0100411968305707</v>
+        <v>0.0006915607955306768</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.01277182996273041</v>
+        <v>0.000363523664418608</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003569703549146652</v>
+        <v>0.0001360105961794034</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01828591339290142</v>
+        <v>0.0008478397503495216</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.00290707778185606</v>
+        <v>0.0004049884155392647</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01179373078048229</v>
+        <v>0.000221030946704559</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.01101460959762335</v>
+        <v>9.64880600804463e-05</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.005616641137748957</v>
+        <v>0.0002693022252060473</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.002075487282127142</v>
+        <v>9.694592154119164e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.007020324934273958</v>
+        <v>0.0003066509962081909</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.002893333090469241</v>
+        <v>5.565561878029257e-06</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.01388417184352875</v>
+        <v>0.0004734784306492656</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01529478188604116</v>
+        <v>0.000503252784255892</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.001743211061693728</v>
+        <v>0.0002978764241561294</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002623022068291903</v>
+        <v>0.000245066185016185</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.007397426757961512</v>
+        <v>0.0002007486764341593</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.004066371358931065</v>
+        <v>0.0004491152067203075</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.004425994586199522</v>
+        <v>0.0003295076894573867</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02841732837259769</v>
+        <v>0.001557456096634269</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.009682255797088146</v>
+        <v>6.090667739044875e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.005857082083821297</v>
+        <v>0.0002448870800435543</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001000773045234382</v>
+        <v>0.0003253172035329044</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002027749549597502</v>
+        <v>0.0002574159298092127</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001105086412280798</v>
+        <v>5.960655107628554e-05</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.008886148221790791</v>
+        <v>0.0003356835804879665</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.004224454052746296</v>
+        <v>0.0002281194756506011</v>
       </c>
       <c r="CD8" t="n">
-        <v>8.003902621567249e-06</v>
+        <v>3.90287023037672e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.01251649763435125</v>
+        <v>0.0007026935345493257</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.005253682378679514</v>
+        <v>7.776597340125591e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.005947345402091742</v>
+        <v>0.0002978567499667406</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.000798103807028383</v>
+        <v>0.0001944567629834637</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002148012397810817</v>
+        <v>0.0002524447627365589</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.007727762684226036</v>
+        <v>0.0001569617888890207</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001690213539404795</v>
+        <v>0.0002010767784668133</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.005000404082238674</v>
+        <v>0.0003345074655953795</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.01655412279069424</v>
+        <v>0.0001671718200668693</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01002239715307951</v>
+        <v>0.001115569495595992</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001393389422446489</v>
+        <v>8.30210919957608e-05</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.006662202998995781</v>
+        <v>0.0001699864806141704</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0168506633490324</v>
+        <v>0.0001477925397921354</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0002839574008248746</v>
+        <v>0.0005118366098031402</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.002694403054192662</v>
+        <v>0.0004340463201515377</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.002220313064754009</v>
+        <v>0.0002270207769470289</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0004665626911446452</v>
+        <v>0.0002033004711847752</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001638761721551418</v>
+        <v>3.145133450743742e-05</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.01208189129829407</v>
+        <v>0.0007711462094448507</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.005656515713781118</v>
+        <v>8.107534813461825e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.01041226461529732</v>
+        <v>0.0002078296092804521</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.001514348550699651</v>
+        <v>0.0001869286206783727</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002499691676348448</v>
+        <v>0.0002425810816930607</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.008736718446016312</v>
+        <v>0.0001919495116453618</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001517163589596748</v>
+        <v>0.0002578346466179937</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.004203967284411192</v>
+        <v>0.0004034805751871318</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.005256431177258492</v>
+        <v>0.0003109137469436973</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02442360483109951</v>
+        <v>0.0001300536969210953</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.003901492804288864</v>
+        <v>0.0004502953379414976</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01962215453386307</v>
+        <v>0.0001120253655244596</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.002254382474347949</v>
+        <v>0.0001926167460624129</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002884042449295521</v>
+        <v>0.0004265870084054768</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.003330346196889877</v>
+        <v>3.534227289492264e-06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.004318314604461193</v>
+        <v>0.0006580242188647389</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.009062415920197964</v>
+        <v>9.172809222945943e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0005669313250109553</v>
+        <v>6.225612014532089e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.004404284525662661</v>
+        <v>0.0002049318718491122</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.003846728475764394</v>
+        <v>6.614689482375979e-06</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0002770876744762063</v>
+        <v>0.0004749644722323865</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0002259204775327817</v>
+        <v>4.143630940234289e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.007233637850731611</v>
+        <v>0.000507572025526315</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.009268053807318211</v>
+        <v>0.0004547392018139362</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.005006723571568727</v>
+        <v>0.0002518061664886773</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.01132050529122353</v>
+        <v>0.0006494146073237062</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001439880579710007</v>
+        <v>0.0001314254914177582</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.004810980521142483</v>
+        <v>0.0002776347391773015</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.008750510402023792</v>
+        <v>0.0001031097999657504</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.007555227261036634</v>
+        <v>0.0004221607523504645</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.006592143792659044</v>
+        <v>0.0003886565973516554</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.00797607097774744</v>
+        <v>0.0007830059621483088</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.001352623337879777</v>
+        <v>0.0001404397480655462</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.004179371986538172</v>
+        <v>0.0002828145516104996</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001697277533821762</v>
+        <v>0.0002900506951846182</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.005872016772627831</v>
+        <v>7.950965664349496e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.003554567694664001</v>
+        <v>0.0008144049206748605</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.003123200731351972</v>
+        <v>0.0001671915670158342</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.009196072816848755</v>
+        <v>3.516318247420713e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003655258624348789</v>
+        <v>0.0001425647496944293</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.003362789284437895</v>
+        <v>0.0001686887699179351</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.005923878867179155</v>
+        <v>6.718511576764286e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.001503650331869721</v>
+        <v>6.783747085137293e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.00204941350966692</v>
+        <v>0.0003305774298496544</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.004654800985008478</v>
+        <v>0.0001236035022884607</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.004486487712711096</v>
+        <v>0.0005172346718609333</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.00780307175591588</v>
+        <v>0.0001123563124565408</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.008400647900998592</v>
+        <v>0.0004031203570775688</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.007361708674579859</v>
+        <v>6.031319935573265e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.006642627529799938</v>
+        <v>0.00014082009147387</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.00795851182192564</v>
+        <v>1.086504562408663e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.006226672325283289</v>
+        <v>7.98229084466584e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.009362535551190376</v>
+        <v>6.02577201789245e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.001895721885375679</v>
+        <v>2.87526345346123e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.01123825088143349</v>
+        <v>0.0008405650150962174</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.003436874831095338</v>
+        <v>9.480162407271564e-05</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.007997914217412472</v>
+        <v>0.0001793300616554916</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.003154310397803783</v>
+        <v>0.0001593073247931898</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.001462590647861362</v>
+        <v>0.0002472655032761395</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.01018988434225321</v>
+        <v>0.0001372989936498925</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001390985795296729</v>
+        <v>0.0002651714021340013</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.005000175908207893</v>
+        <v>0.0003931177197955549</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.004867156501859426</v>
+        <v>0.000469689373858273</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.01179278083145618</v>
+        <v>0.000295525387628004</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.008075185120105743</v>
+        <v>0.0004862427595071495</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.00203756894916296</v>
+        <v>0.0003327156882733107</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.004984760656952858</v>
+        <v>7.570635352749377e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0005848949076607823</v>
+        <v>0.0005785080720670521</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.002052352298051119</v>
+        <v>3.128087337245233e-05</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.005738188978284597</v>
+        <v>0.0004799879097845405</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.009769227355718613</v>
+        <v>0.0009665508987382054</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.006421963218599558</v>
+        <v>0.00035867840051651</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01212932541966438</v>
+        <v>0.00135860696900636</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.003591637592762709</v>
+        <v>0.000717224320396781</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.01632042229175568</v>
+        <v>0.0006720760720781982</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.007776805199682713</v>
+        <v>0.0004474114102777094</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.01544382702559233</v>
+        <v>0.0008847230346873403</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.005525989457964897</v>
+        <v>0.0003314415225759149</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.006826001219451427</v>
+        <v>0.0007695552776567638</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.006988033652305603</v>
+        <v>0.000528071541339159</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.01204719766974449</v>
+        <v>5.0034392188536e-05</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.006097020581364632</v>
+        <v>0.0006369313923642039</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0004247152828611434</v>
+        <v>0.0003782746207434684</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.006261010188609362</v>
+        <v>0.000299117062240839</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.01583071239292622</v>
+        <v>0.001163062872365117</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.006297079846262932</v>
+        <v>4.489484126679599e-07</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.02007991634309292</v>
+        <v>0.0001138834486482665</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.005366129800677299</v>
+        <v>1.067332959792111e-05</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.006145531311631203</v>
+        <v>1.329242149950005e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.02638169750571251</v>
+        <v>0.08843234926462173</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1381005495786667</v>
+        <v>0.2903520464897156</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02170850522816181</v>
+        <v>0.06461240351200104</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02795634418725967</v>
+        <v>0.01334440615028143</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04760324582457542</v>
+        <v>0.1141081973910332</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006263069342821836</v>
+        <v>0.159001424908638</v>
       </c>
       <c r="G9" t="n">
-        <v>0.028009083122015</v>
+        <v>0.04876236617565155</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01248601730912924</v>
+        <v>0.08649063855409622</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05048311501741409</v>
+        <v>0.03789591044187546</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03060773946344852</v>
+        <v>0.03272849693894386</v>
       </c>
       <c r="K9" t="n">
-        <v>0.106024332344532</v>
+        <v>0.3611272573471069</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01435147318989038</v>
+        <v>0.06374991685152054</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03666195273399353</v>
+        <v>0.09851792454719543</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06656590104103088</v>
+        <v>0.1680275350809097</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02295992150902748</v>
+        <v>0.1563556492328644</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01637142337858677</v>
+        <v>0.06584151834249496</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.006837945431470871</v>
+        <v>0.003305534832179546</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04091234877705574</v>
+        <v>0.03100139833986759</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003505364758893847</v>
+        <v>0.01363109424710274</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02793814614415169</v>
+        <v>0.05590901896357536</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01418139319866896</v>
+        <v>0.001894958782941103</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01398956030607224</v>
+        <v>0.08923794329166412</v>
       </c>
       <c r="W9" t="n">
-        <v>0.006541127804666758</v>
+        <v>0.05475817620754242</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009869223460555077</v>
+        <v>0.04297704249620438</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01037963107228279</v>
+        <v>0.004257173277437687</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001695226179435849</v>
+        <v>0.008947667665779591</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01084837131202221</v>
+        <v>0.03647695481777191</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02183464169502258</v>
+        <v>0.02441355586051941</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03316264227032661</v>
+        <v>0.03464153781533241</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01090404391288757</v>
+        <v>0.05839657783508301</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001627233810722828</v>
+        <v>0.05020738020539284</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01117252465337515</v>
+        <v>0.08121126890182495</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0173327811062336</v>
+        <v>0.07280495017766953</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.005927152931690216</v>
+        <v>0.009337777271866798</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01172339171171188</v>
+        <v>0.1333495676517487</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002023837529122829</v>
+        <v>0.001071326201781631</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01147243566811085</v>
+        <v>0.00964859314262867</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01952119171619415</v>
+        <v>0.1143580973148346</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01050399616360664</v>
+        <v>0.03407338261604309</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001567675732076168</v>
+        <v>0.03533897176384926</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.006391385104507208</v>
+        <v>0.07462622970342636</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.01990148983895779</v>
+        <v>0.03992435708642006</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.009837944060564041</v>
+        <v>0.004227699246257544</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.006646727211773396</v>
+        <v>0.04553130269050598</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.006745255086570978</v>
+        <v>0.01064715068787336</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.005278685130178928</v>
+        <v>0.00489190686494112</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0931229293346405</v>
+        <v>0.3866130709648132</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0106997974216938</v>
+        <v>0.0123111829161644</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.00439627468585968</v>
+        <v>0.01609981060028076</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.005013254471123219</v>
+        <v>0.06077448651194572</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.009014843963086605</v>
+        <v>0.1000592783093452</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02187421545386314</v>
+        <v>0.02623794972896576</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01375751849263906</v>
+        <v>0.01774798892438412</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.005832364782691002</v>
+        <v>0.0110193807631731</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.01135450415313244</v>
+        <v>0.09128820151090622</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03308910876512527</v>
+        <v>0.09025002270936966</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.01972637139260769</v>
+        <v>0.08219222724437714</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00878443755209446</v>
+        <v>0.02770065143704414</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0510270968079567</v>
+        <v>0.09438832849264145</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.01555666700005531</v>
+        <v>0.01325049344450235</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01099413260817528</v>
+        <v>0.0224272795021534</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003944078925997019</v>
+        <v>0.02346275374293327</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0250767357647419</v>
+        <v>0.007505213376134634</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.01674451865255833</v>
+        <v>0.01806183904409409</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.005608344450592995</v>
+        <v>0.04920945316553116</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.001372253987938166</v>
+        <v>0.00627099396660924</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02365433052182198</v>
+        <v>0.0541040375828743</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.03543695062398911</v>
+        <v>0.04575621336698532</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.02900507487356663</v>
+        <v>0.02425852231681347</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00376034202054143</v>
+        <v>0.1318880468606949</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.006075744517147541</v>
+        <v>0.02114641666412354</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.006027309689670801</v>
+        <v>0.00307477405294776</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.006107655353844166</v>
+        <v>0.02129774168133736</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.05891247466206551</v>
+        <v>0.2506656646728516</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01863001100718975</v>
+        <v>0.02096496149897575</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.008730081841349602</v>
+        <v>0.1020420119166374</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0009706891141831875</v>
+        <v>0.0585862509906292</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.008724164217710495</v>
+        <v>0.06934698671102524</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.007277193013578653</v>
+        <v>0.03220828622579575</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.01193704549223185</v>
+        <v>0.002266544383019209</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0121668791398406</v>
+        <v>0.03401569277048111</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001213258015923202</v>
+        <v>0.001127813942730427</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0262223593890667</v>
+        <v>0.1134069338440895</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0006281975074671209</v>
+        <v>0.02506553381681442</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002317177364602685</v>
+        <v>0.003161621745675802</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0008515879744663835</v>
+        <v>0.01649558171629906</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002435804344713688</v>
+        <v>0.03738494962453842</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001259803306311369</v>
+        <v>0.02593204937875271</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001125571085140109</v>
+        <v>0.006200449541211128</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.01406137458980083</v>
+        <v>0.002496182452887297</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0375424437224865</v>
+        <v>0.06715165078639984</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03812947869300842</v>
+        <v>0.1922687292098999</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001910649472847581</v>
+        <v>0.09781741350889206</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.00429565878584981</v>
+        <v>0.09197275340557098</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0007239821134135127</v>
+        <v>0.05155346542596817</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0004667090252041817</v>
+        <v>0.002817119937390089</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.02075593918561935</v>
+        <v>0.06826449930667877</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.03065007552504539</v>
+        <v>0.004361856728792191</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0005817064084112644</v>
+        <v>0.009768003597855568</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.001411077566444874</v>
+        <v>0.02088038623332977</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.02317375689744949</v>
+        <v>0.1008135974407196</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.004101711791008711</v>
+        <v>0.0257654432207346</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.003279739757999778</v>
+        <v>0.01458789594471455</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.003003102261573076</v>
+        <v>0.01155791524797678</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.00183054618537426</v>
+        <v>0.03532824292778969</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001665211748331785</v>
+        <v>0.01074074395000935</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0007390970131382346</v>
+        <v>0.001878066686913371</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.009107289835810661</v>
+        <v>0.01193240284919739</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003416450694203377</v>
+        <v>0.116784542798996</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.03391409292817116</v>
+        <v>0.06187624111771584</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.01469886023551226</v>
+        <v>0.004037691280245781</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02375327609479427</v>
+        <v>0.1282217651605606</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.007962453179061413</v>
+        <v>0.005492636933922768</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.003450471209362149</v>
+        <v>0.09298396110534668</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.02211124263703823</v>
+        <v>0.03867389261722565</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.003940454684197903</v>
+        <v>0.1055578738451004</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.008871002122759819</v>
+        <v>0.01464410126209259</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002413520822301507</v>
+        <v>0.0005229203961789608</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.007504138629883528</v>
+        <v>0.0311884693801403</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.007612257264554501</v>
+        <v>0.021367147564888</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.007347287610173225</v>
+        <v>0.06518666446208954</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.002905009314417839</v>
+        <v>0.01741625741124153</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.004829124081879854</v>
+        <v>0.01201807521283627</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.01815426163375378</v>
+        <v>0.00568711943924427</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.00515022361651063</v>
+        <v>0.04860223084688187</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.002322268672287464</v>
+        <v>0.02204685099422932</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.001184798311442137</v>
+        <v>0.02863839454948902</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01223612017929554</v>
+        <v>0.09076680243015289</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.000684474129229784</v>
+        <v>0.05029405653476715</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.305164187215269e-05</v>
+        <v>0.012517424300313</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.009605107828974724</v>
+        <v>0.09199071675539017</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.003113957587629557</v>
+        <v>0.07650047540664673</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.00399741530418396</v>
+        <v>0.01992849633097649</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.02333650179207325</v>
+        <v>0.07330633699893951</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.006719944998621941</v>
+        <v>0.05332403630018234</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.004128623753786087</v>
+        <v>0.02714146487414837</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.01101913210004568</v>
+        <v>0.0219638142734766</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001321070827543736</v>
+        <v>0.0163249708712101</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.01132386457175016</v>
+        <v>0.02048406563699245</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.008086150512099266</v>
+        <v>0.01776897348463535</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.003908899147063494</v>
+        <v>0.04457949101924896</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.01167917996644974</v>
+        <v>0.004351564683020115</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003938049776479602</v>
+        <v>0.01022862363606691</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.01743280701339245</v>
+        <v>0.007660411298274994</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.01209840551018715</v>
+        <v>0.001996561884880066</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0264244619756937</v>
+        <v>0.07616178691387177</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.01263107545673847</v>
+        <v>0.05025208368897438</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.00496992189437151</v>
+        <v>0.03853582963347435</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.002928606467321515</v>
+        <v>0.04435159265995026</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003136508632451296</v>
+        <v>0.01448003388941288</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.006861296482384205</v>
+        <v>0.02826939150691032</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.003606870770454407</v>
+        <v>0.03208256140351295</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.005860562436282635</v>
+        <v>0.0286607313901186</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0002622977190185338</v>
+        <v>0.006063698790967464</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.02743009477853775</v>
+        <v>0.1256398558616638</v>
       </c>
       <c r="EZ9" t="n">
-        <v>9.215943282470107e-05</v>
+        <v>0.02674368768930435</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001770790317095816</v>
+        <v>0.01779945567250252</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.003057426540181041</v>
+        <v>0.006291798315942287</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.005230897571891546</v>
+        <v>0.03995002433657646</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0001191073097288609</v>
+        <v>0.02800252102315426</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.002831256482750177</v>
+        <v>0.002186496276408434</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.008041288703680038</v>
+        <v>0.01734969019889832</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0007863603532314301</v>
+        <v>0.0365954227745533</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0120293851941824</v>
+        <v>0.05931297317147255</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.009794740006327629</v>
+        <v>0.002596828155219555</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.01015857420861721</v>
+        <v>0.06987936049699783</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.009985265322029591</v>
+        <v>0.03695173189043999</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0008652890101075172</v>
+        <v>0.01968766935169697</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.00597020611166954</v>
+        <v>0.01845169626176357</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.007539165671914816</v>
+        <v>0.06112337857484818</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.01604060083627701</v>
+        <v>0.01218864414840937</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.01360338553786278</v>
+        <v>0.08469104021787643</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.01331809535622597</v>
+        <v>0.1175504177808762</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.01180979888886213</v>
+        <v>0.01863805204629898</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.00297286082059145</v>
+        <v>0.02363517694175243</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.01033383794128895</v>
+        <v>0.1097791120409966</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01068012230098248</v>
+        <v>0.02466550096869469</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.02002562209963799</v>
+        <v>0.01529748737812042</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.02476439066231251</v>
+        <v>0.02254838868975639</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.01146345585584641</v>
+        <v>0.02387835644185543</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.02097207494080067</v>
+        <v>0.01078004762530327</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.01473355945199728</v>
+        <v>0.01730776205658913</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.008245114237070084</v>
+        <v>0.02912875078618526</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.009889477863907814</v>
+        <v>0.00685293460264802</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.01878736168146133</v>
+        <v>0.04281814023852348</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.02372186258435249</v>
+        <v>0.05358671396970749</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.02187224477529526</v>
+        <v>0.009233029559254646</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.01612873189151287</v>
+        <v>0.04734225943684578</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.004625734873116016</v>
+        <v>0.03211415186524391</v>
       </c>
     </row>
     <row r="10">
@@ -6120,2278 +6120,2278 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.05087659507989883</v>
+        <v>0.2956071197986603</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6551549434661865</v>
+        <v>0.2097222208976746</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5674992799758911</v>
+        <v>0.5267529487609863</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2443849295377731</v>
+        <v>0.6589598059654236</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7310421466827393</v>
+        <v>0.4009454846382141</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07958438992500305</v>
+        <v>0.06672003865242004</v>
       </c>
       <c r="G11" t="n">
-        <v>0.279327392578125</v>
+        <v>0.1810636818408966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2367377281188965</v>
+        <v>0.0904914066195488</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3321493566036224</v>
+        <v>0.1263859272003174</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1313386261463165</v>
+        <v>0.270944356918335</v>
       </c>
       <c r="K11" t="n">
-        <v>0.466825544834137</v>
+        <v>0.4254042506217957</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3783947825431824</v>
+        <v>0.3758119940757751</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1917919367551804</v>
+        <v>0.5662096738815308</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8066661953926086</v>
+        <v>0.2903485298156738</v>
       </c>
       <c r="O11" t="n">
-        <v>0.126898393034935</v>
+        <v>0.1929424703121185</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2723886370658875</v>
+        <v>0.1990344524383545</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1594605892896652</v>
+        <v>0.0314088836312294</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2525058090686798</v>
+        <v>0.1766329705715179</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02855133265256882</v>
+        <v>0.1575530022382736</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1152994111180305</v>
+        <v>0.2959610819816589</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007808821275830269</v>
+        <v>0.3718747198581696</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1589225828647614</v>
+        <v>0.1274172365665436</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1012454107403755</v>
+        <v>0.08791451901197433</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1490786224603653</v>
+        <v>0.1531151831150055</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.004327455535531044</v>
+        <v>0.02875912562012672</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1286806166172028</v>
+        <v>0.1173782348632812</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.07079032808542252</v>
+        <v>0.1134361550211906</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.07417525351047516</v>
+        <v>0.2290864139795303</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1701214760541916</v>
+        <v>0.07470604032278061</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.003837145864963531</v>
+        <v>0.3653550744056702</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1107606291770935</v>
+        <v>0.08105684816837311</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.05915375798940659</v>
+        <v>0.04542502760887146</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1247408464550972</v>
+        <v>0.08229652047157288</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0136243924498558</v>
+        <v>0.02987766265869141</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.06574058532714844</v>
+        <v>0.2509883642196655</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02492513135075569</v>
+        <v>0.1377080976963043</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.006663396954536438</v>
+        <v>0.1465889811515808</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.3569846749305725</v>
+        <v>0.475545346736908</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.004030823707580566</v>
+        <v>0.04238261282444</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.06992025673389435</v>
+        <v>0.06467325240373611</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.009083693847060204</v>
+        <v>0.4654800295829773</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.1487974226474762</v>
+        <v>0.03846336528658867</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.02254658192396164</v>
+        <v>0.06266280263662338</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.03750970214605331</v>
+        <v>0.01202301494777203</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.1108453348278999</v>
+        <v>0.04379170387983322</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.1803907006978989</v>
+        <v>0.1735562086105347</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5895699262619019</v>
+        <v>0.483345091342926</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.3790908753871918</v>
+        <v>0.2867020666599274</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0575115866959095</v>
+        <v>0.4015323221683502</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1414304226636887</v>
+        <v>0.6068621873855591</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1834969967603683</v>
+        <v>0.1208071559667587</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.01015175879001617</v>
+        <v>0.04079088196158409</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.011645233258605</v>
+        <v>0.3381299376487732</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.1124794781208038</v>
+        <v>0.1412918716669083</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0431271605193615</v>
+        <v>0.1455797255039215</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03053856641054153</v>
+        <v>0.8822528123855591</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.05798040330410004</v>
+        <v>0.5593940019607544</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.2798956632614136</v>
+        <v>0.03164126351475716</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.6100434064865112</v>
+        <v>1.397466778755188</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.03262158110737801</v>
+        <v>0.1293768137693405</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.1656705737113953</v>
+        <v>0.1529793739318848</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.07732705026865005</v>
+        <v>0.2975718080997467</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.1641398519277573</v>
+        <v>0.09394967555999756</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.2245603054761887</v>
+        <v>0.1930830478668213</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.2150991857051849</v>
+        <v>0.02828101813793182</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.05522866547107697</v>
+        <v>0.1822481900453568</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0587795153260231</v>
+        <v>0.04017169401049614</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1237502098083496</v>
+        <v>0.1148371398448944</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.1589523255825043</v>
+        <v>0.1279436051845551</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.1490662693977356</v>
+        <v>0.06856667250394821</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.09714406728744507</v>
+        <v>0.03930354863405228</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.1061887145042419</v>
+        <v>0.1029217913746834</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1371117234230042</v>
+        <v>0.2878467440605164</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.3253659605979919</v>
+        <v>0.6190174221992493</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.3999916911125183</v>
+        <v>0.3027207553386688</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.005585707724094391</v>
+        <v>0.08227820694446564</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1146147325634956</v>
+        <v>0.1057926341891289</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.1014298796653748</v>
+        <v>0.2875040471553802</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0402594730257988</v>
+        <v>0.08272229135036469</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.03187799453735352</v>
+        <v>0.02126302942633629</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.009496085345745087</v>
+        <v>0.05293795466423035</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.005182996392250061</v>
+        <v>0.1782946437597275</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.09676089882850647</v>
+        <v>0.2129542529582977</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.07527307420969009</v>
+        <v>0.108192652463913</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.1311590522527695</v>
+        <v>0.1204595863819122</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.1575766354799271</v>
+        <v>0.07461127638816833</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03721575811505318</v>
+        <v>5.357712507247925e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001892564352601767</v>
+        <v>0.04361782968044281</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.06878098100423813</v>
+        <v>0.05271559953689575</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.07268635183572769</v>
+        <v>0.01039471291005611</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.1553008109331131</v>
+        <v>0.1754097938537598</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.1105695888400078</v>
+        <v>0.1493643224239349</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.02541904337704182</v>
+        <v>0.136192575097084</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.2425942271947861</v>
+        <v>0.3277369141578674</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.2039075642824173</v>
+        <v>0.7248969674110413</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.1053209602832794</v>
+        <v>0.2206081598997116</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.14927938580513</v>
+        <v>0.1120670214295387</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.06514639407396317</v>
+        <v>0.1484841108322144</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.05760979279875755</v>
+        <v>0.006742604076862335</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.02922976016998291</v>
+        <v>0.1385423690080643</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.02999508753418922</v>
+        <v>0.1613538563251495</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.06534281373023987</v>
+        <v>0.1130383536219597</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.1060666590929031</v>
+        <v>0.07231292128562927</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.129588320851326</v>
+        <v>0.07916752994060516</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.05452645197510719</v>
+        <v>0.06770159304141998</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.006788872182369232</v>
+        <v>0.06051571667194366</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.03634814918041229</v>
+        <v>0.09207994490861893</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.127794086933136</v>
+        <v>0.0857095867395401</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1504220068454742</v>
+        <v>0.1791310012340546</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.05551958084106445</v>
+        <v>0.2234741747379303</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.1118040233850479</v>
+        <v>0.3577977120876312</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.313539445400238</v>
+        <v>0.1020399779081345</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03317458182573318</v>
+        <v>0.02798650041222572</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.06216038390994072</v>
+        <v>0.5481149554252625</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.08455443382263184</v>
+        <v>0.07679139077663422</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.1646832972764969</v>
+        <v>0.1235490888357162</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.1734495460987091</v>
+        <v>0.3839857280254364</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.09073086082935333</v>
+        <v>0.182063564658165</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.03581081703305244</v>
+        <v>0.09976625442504883</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.04676191508769989</v>
+        <v>0.02990041300654411</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.1062984466552734</v>
+        <v>0.1913415789604187</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.1561384946107864</v>
+        <v>0.1405749469995499</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1888758391141891</v>
+        <v>0.2122303247451782</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.02415505982935429</v>
+        <v>0.02964574843645096</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.03749634698033333</v>
+        <v>0.1021972745656967</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.04469552263617516</v>
+        <v>0.08621394634246826</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.07998201251029968</v>
+        <v>0.08343725651502609</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1005874872207642</v>
+        <v>0.3097074627876282</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.09500700235366821</v>
+        <v>0.03089131414890289</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.07233388721942902</v>
+        <v>0.2430682182312012</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.1225016638636589</v>
+        <v>0.5633408427238464</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.2058645933866501</v>
+        <v>0.0520835816860199</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.01248658169060946</v>
+        <v>0.03888415545225143</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.07837804406881332</v>
+        <v>0.07272306829690933</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01626089215278625</v>
+        <v>0.0886707529425621</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.03519788384437561</v>
+        <v>0.1450945734977722</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.05209698528051376</v>
+        <v>0.01136776804924011</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.04099832475185394</v>
+        <v>0.01367053389549255</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.05698300525546074</v>
+        <v>0.04062521085143089</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.1936584562063217</v>
+        <v>0.005801025778055191</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.04288386553525925</v>
+        <v>0.01385165564715862</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.09687155485153198</v>
+        <v>0.03340959548950195</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.02353386580944061</v>
+        <v>0.1138632819056511</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.1337963044643402</v>
+        <v>0.141795352101326</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.05121636763215065</v>
+        <v>0.005607975646853447</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.04193691909313202</v>
+        <v>0.2470362484455109</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0941179096698761</v>
+        <v>0.2668220698833466</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.1078903749585152</v>
+        <v>0.04933926835656166</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.03584827482700348</v>
+        <v>0.07747944444417953</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.2015871703624725</v>
+        <v>0.0001887902617454529</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.08830837160348892</v>
+        <v>0.06691525876522064</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.1253560036420822</v>
+        <v>0.1440747678279877</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.2597638070583344</v>
+        <v>0.1134090796113014</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.006284326314926147</v>
+        <v>0.2064187526702881</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.01666093617677689</v>
+        <v>0.1679784804582596</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.06052092090249062</v>
+        <v>0.0819430872797966</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.1433342844247818</v>
+        <v>0.1260117292404175</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.1427036672830582</v>
+        <v>0.1086092814803123</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0803791880607605</v>
+        <v>0.09681946784257889</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.03324206918478012</v>
+        <v>0.0298017542809248</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.1015682891011238</v>
+        <v>0.09976047277450562</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.05603266134858131</v>
+        <v>0.05500089377164841</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.05391434580087662</v>
+        <v>0.06035315990447998</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.2170421779155731</v>
+        <v>0.2608437836170197</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.1610262095928192</v>
+        <v>0.3459382355213165</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0692000687122345</v>
+        <v>0.002262741327285767</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.1508391499519348</v>
+        <v>0.4723259210586548</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.008993562310934067</v>
+        <v>0.5071651339530945</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.156096339225769</v>
+        <v>0.007570497691631317</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.01165476627647877</v>
+        <v>0.1440925449132919</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.1292327493429184</v>
+        <v>0.232509583234787</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.008302941918373108</v>
+        <v>0.1867574751377106</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.1076796129345894</v>
+        <v>0.5298460125923157</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.2010010480880737</v>
+        <v>0.2371300458908081</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.3002151250839233</v>
+        <v>0.1869992017745972</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.03944172710180283</v>
+        <v>0.3470439612865448</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02006193809211254</v>
+        <v>0.6564397811889648</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.1319470703601837</v>
+        <v>0.07823626697063446</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.2409802228212357</v>
+        <v>0.04030001908540726</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01767439022660255</v>
+        <v>0.03745275735855103</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.1085974276065826</v>
+        <v>0.0450814962387085</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.06191705912351608</v>
+        <v>0.1747282892465591</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.1324360966682434</v>
+        <v>0.1795162111520767</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.06201763823628426</v>
+        <v>0.2364161610603333</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.09203535318374634</v>
+        <v>0.00696660578250885</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.2361350208520889</v>
+        <v>0.3875554203987122</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1564380675554276</v>
+        <v>0.02385037019848824</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.4043647348880768</v>
+        <v>0.1247090697288513</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.08564833551645279</v>
+        <v>0.09568849951028824</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0001171166441054083</v>
+        <v>6.450891669373959e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001237048185430467</v>
+        <v>0.03261193633079529</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001067018674802966</v>
+        <v>0.0148157374933362</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004314736288506538</v>
+        <v>0.009803183376789093</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0003088231314904988</v>
+        <v>0.007461476139724255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0006134618306532502</v>
+        <v>0.02278399094939232</v>
       </c>
       <c r="G12" t="n">
-        <v>5.732083081966266e-05</v>
+        <v>0.006443632766604424</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003735339269042015</v>
+        <v>0.007353258784860373</v>
       </c>
       <c r="I12" t="n">
-        <v>6.168369509396143e-06</v>
+        <v>0.01509168464690447</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000218141358345747</v>
+        <v>0.002680992009118199</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001158298342488706</v>
+        <v>0.03197450190782547</v>
       </c>
       <c r="L12" t="n">
-        <v>1.446435453544836e-05</v>
+        <v>0.02154011465609074</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002432382898405194</v>
+        <v>0.02694818004965782</v>
       </c>
       <c r="N12" t="n">
-        <v>1.148731826106086e-06</v>
+        <v>0.002372649498283863</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0006787022575736046</v>
+        <v>0.0289232861250639</v>
       </c>
       <c r="P12" t="n">
-        <v>7.027263927739114e-05</v>
+        <v>0.00821941252797842</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001337644644081593</v>
+        <v>0.0007522674277424812</v>
       </c>
       <c r="R12" t="n">
-        <v>3.434595419093966e-05</v>
+        <v>0.01967684179544449</v>
       </c>
       <c r="S12" t="n">
-        <v>4.552691098069772e-05</v>
+        <v>0.005132936872541904</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0001019271439872682</v>
+        <v>0.007159569300711155</v>
       </c>
       <c r="U12" t="n">
-        <v>6.771088374080136e-05</v>
+        <v>0.003238328266888857</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0001876055321190506</v>
+        <v>0.001620011869817972</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0001159649837063625</v>
+        <v>0.004558240994811058</v>
       </c>
       <c r="X12" t="n">
-        <v>6.212814696482383e-06</v>
+        <v>0.002088551176711917</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.402502832410391e-05</v>
+        <v>0.006049223244190216</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0001151540491264313</v>
+        <v>0.00212807534262538</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.298263618489727e-05</v>
+        <v>0.003804826410487294</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.940578658832237e-05</v>
+        <v>0.004214445129036903</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.087259988707956e-05</v>
+        <v>0.0008902432164177299</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.072104638908058e-05</v>
+        <v>0.007190936245024204</v>
       </c>
       <c r="AE12" t="n">
-        <v>9.967650839826092e-05</v>
+        <v>0.007986921817064285</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.171065903501585e-05</v>
+        <v>0.01047243736684322</v>
       </c>
       <c r="AG12" t="n">
-        <v>9.97924325929489e-06</v>
+        <v>0.01429695636034012</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.886056452349294e-05</v>
+        <v>0.003449574811384082</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.00010916428436758</v>
+        <v>0.02384053356945515</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.179049134720117e-05</v>
+        <v>0.0003467149799689651</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0002299183834111318</v>
+        <v>0.003320765215903521</v>
       </c>
       <c r="AL12" t="n">
-        <v>8.248706581071019e-05</v>
+        <v>0.00529630109667778</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.746865382301621e-05</v>
+        <v>0.0006982332561165094</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.815226803766564e-06</v>
+        <v>0.002923974767327309</v>
       </c>
       <c r="AO12" t="n">
-        <v>6.595397280761972e-05</v>
+        <v>0.007218272890895605</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0001731083902996033</v>
+        <v>0.002600452397018671</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.989786248188466e-05</v>
+        <v>0.0002487649326212704</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0001092257371055894</v>
+        <v>0.007076353300362825</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001408308889949694</v>
+        <v>0.002587185706943274</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.921795021393336e-05</v>
+        <v>0.005858135409653187</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.000686386541929096</v>
+        <v>0.03017770126461983</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001776876015355811</v>
+        <v>0.009323012083768845</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.172630749759264e-05</v>
+        <v>0.009552048519253731</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0002155125694116578</v>
+        <v>0.02012882381677628</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0002793985768221319</v>
+        <v>0.02282928489148617</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8.236093708546832e-05</v>
+        <v>0.002349377376958728</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0001498496276326478</v>
+        <v>0.008714592084288597</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0001002957942546345</v>
+        <v>0.002513691317290068</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.35571967298165e-05</v>
+        <v>0.005796131677925587</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.000255537626799196</v>
+        <v>0.00336635927669704</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0003351273480802774</v>
+        <v>0.01164150424301624</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.310872489237227e-05</v>
+        <v>0.00426699873059988</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.064659050432965e-05</v>
+        <v>0.01656481251120567</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0001000667907646857</v>
+        <v>0.003680491354316473</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0001175436555058695</v>
+        <v>0.007365399040281773</v>
       </c>
       <c r="BJ12" t="n">
-        <v>5.158224666956812e-05</v>
+        <v>0.001961924834176898</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.267237090971321e-05</v>
+        <v>0.009988238103687763</v>
       </c>
       <c r="BL12" t="n">
-        <v>8.67922353791073e-05</v>
+        <v>0.0002412336179986596</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001645397569518536</v>
+        <v>0.01067366451025009</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001411358680343255</v>
+        <v>0.005735649261623621</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.725633723661304e-05</v>
+        <v>0.002897663973271847</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.047788388561457e-05</v>
+        <v>0.005562174133956432</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.611511419876479e-05</v>
+        <v>0.004375656135380268</v>
       </c>
       <c r="BR12" t="n">
-        <v>7.142277172533795e-05</v>
+        <v>0.004331436473876238</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.146472828229889e-05</v>
+        <v>0.001706309500150383</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0001771178212948143</v>
+        <v>0.0026514264754951</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.812959403148852e-05</v>
+        <v>0.002418969292193651</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0004195033689029515</v>
+        <v>0.01717999763786793</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001338043803116307</v>
+        <v>0.004137756302952766</v>
       </c>
       <c r="BX12" t="n">
-        <v>1.615720975678414e-05</v>
+        <v>0.003528164932504296</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.103412594413385e-05</v>
+        <v>0.004085303284227848</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0001687228505034</v>
+        <v>0.00911472924053669</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.878321356547531e-05</v>
+        <v>0.01079789269715548</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.570114080910571e-05</v>
+        <v>0.001182300271466374</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.579787855618633e-05</v>
+        <v>0.005691076628863811</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.315476326155476e-05</v>
+        <v>0.0002508106990717351</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0002360898215556517</v>
+        <v>0.01107136625796556</v>
       </c>
       <c r="CF12" t="n">
-        <v>9.1514055384323e-05</v>
+        <v>0.005064566619694233</v>
       </c>
       <c r="CG12" t="n">
-        <v>7.011259731370956e-05</v>
+        <v>0.003586011473089457</v>
       </c>
       <c r="CH12" t="n">
-        <v>5.832851456943899e-05</v>
+        <v>0.0006316102808341384</v>
       </c>
       <c r="CI12" t="n">
-        <v>4.306236587581225e-05</v>
+        <v>0.00453645084053278</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.251956074265763e-05</v>
+        <v>0.0002871012839023024</v>
       </c>
       <c r="CK12" t="n">
-        <v>8.669171074870974e-05</v>
+        <v>0.0006858757697045803</v>
       </c>
       <c r="CL12" t="n">
-        <v>6.106386717874557e-05</v>
+        <v>0.002086003310978413</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0002791569568216801</v>
+        <v>0.004805959761142731</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0001084002433344722</v>
+        <v>0.003412917722016573</v>
       </c>
       <c r="CO12" t="n">
-        <v>5.603586487268331e-06</v>
+        <v>0.009644506499171257</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0002151614025933668</v>
+        <v>0.0124169671908021</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0001465432142140344</v>
+        <v>0.005693668499588966</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0003277101495768875</v>
+        <v>0.002700289944186807</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0002248292585136369</v>
+        <v>0.006489779334515333</v>
       </c>
       <c r="CT12" t="n">
-        <v>6.952360126888379e-05</v>
+        <v>0.002155381953343749</v>
       </c>
       <c r="CU12" t="n">
-        <v>5.762340151704848e-05</v>
+        <v>0.006497327238321304</v>
       </c>
       <c r="CV12" t="n">
-        <v>3.773729258682579e-05</v>
+        <v>0.002491294406354427</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0002261948538944125</v>
+        <v>0.008660925552248955</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0001248415355803445</v>
+        <v>0.006778721697628498</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.000122028446639888</v>
+        <v>0.00521854730322957</v>
       </c>
       <c r="CZ12" t="n">
-        <v>5.122640504851006e-05</v>
+        <v>0.0007996554486453533</v>
       </c>
       <c r="DA12" t="n">
-        <v>6.338359526125714e-05</v>
+        <v>0.007722056936472654</v>
       </c>
       <c r="DB12" t="n">
-        <v>5.995520405122079e-05</v>
+        <v>0.001735553843900561</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0001494045718573034</v>
+        <v>0.0007644675788469613</v>
       </c>
       <c r="DD12" t="n">
-        <v>5.021639663027599e-05</v>
+        <v>0.003057485911995173</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0001370056997984648</v>
+        <v>0.0008778998162597418</v>
       </c>
       <c r="DF12" t="n">
-        <v>6.6605512984097e-05</v>
+        <v>0.01817023567855358</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.331540822022362e-06</v>
+        <v>0.01512507721781731</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0004261558351572603</v>
+        <v>0.0001692943624220788</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0004867747484240681</v>
+        <v>0.005357318092137575</v>
       </c>
       <c r="DJ12" t="n">
-        <v>8.768583938945085e-05</v>
+        <v>0.01782485283911228</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0001551551395095885</v>
+        <v>0.005678699351847172</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0001668906043050811</v>
+        <v>0.009497806429862976</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0001775909477146342</v>
+        <v>0.0005609606159850955</v>
       </c>
       <c r="DN12" t="n">
-        <v>7.034532609395683e-05</v>
+        <v>0.002195702865719795</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001335168199148029</v>
+        <v>0.008114300668239594</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.827017154544592e-05</v>
+        <v>0.004048534668982029</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0001425681984983385</v>
+        <v>0.008565829135477543</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.019356128992513e-05</v>
+        <v>0.0001300816657021642</v>
       </c>
       <c r="DS12" t="n">
-        <v>9.399465488968417e-05</v>
+        <v>0.004869308788329363</v>
       </c>
       <c r="DT12" t="n">
-        <v>5.445639544632286e-05</v>
+        <v>0.002665768377482891</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0001296676200581715</v>
+        <v>0.01015174202620983</v>
       </c>
       <c r="DV12" t="n">
-        <v>5.699021494365297e-05</v>
+        <v>0.004803964402526617</v>
       </c>
       <c r="DW12" t="n">
-        <v>3.70309135178104e-06</v>
+        <v>0.0006172927096486092</v>
       </c>
       <c r="DX12" t="n">
-        <v>5.746578608523123e-05</v>
+        <v>0.008592592552304268</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0001308555947616696</v>
+        <v>0.01233669370412827</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.62122048297897e-05</v>
+        <v>0.002585174050182104</v>
       </c>
       <c r="EA12" t="n">
-        <v>7.160037057474256e-05</v>
+        <v>0.007061610464006662</v>
       </c>
       <c r="EB12" t="n">
-        <v>4.216229353914969e-05</v>
+        <v>0.003841590136289597</v>
       </c>
       <c r="EC12" t="n">
-        <v>9.528168448014185e-05</v>
+        <v>0.012037243694067</v>
       </c>
       <c r="ED12" t="n">
-        <v>2.266719457111321e-05</v>
+        <v>0.005447434261441231</v>
       </c>
       <c r="EE12" t="n">
-        <v>8.482078555971384e-05</v>
+        <v>0.01784889400005341</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0002097113756462932</v>
+        <v>0.000280670530628413</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0002718578616622835</v>
+        <v>0.001828609616495669</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0001542687678011134</v>
+        <v>0.0006986712105572224</v>
       </c>
       <c r="EI12" t="n">
-        <v>7.639691466465592e-05</v>
+        <v>0.01022890489548445</v>
       </c>
       <c r="EJ12" t="n">
-        <v>6.392368231900036e-05</v>
+        <v>0.0005076772067695856</v>
       </c>
       <c r="EK12" t="n">
-        <v>5.531381611945108e-05</v>
+        <v>0.0009288747096434236</v>
       </c>
       <c r="EL12" t="n">
-        <v>4.676752723753452e-05</v>
+        <v>0.0029989427421242</v>
       </c>
       <c r="EM12" t="n">
-        <v>3.519750316627324e-05</v>
+        <v>0.003488517832010984</v>
       </c>
       <c r="EN12" t="n">
-        <v>1.894168417493347e-05</v>
+        <v>0.01030332408845425</v>
       </c>
       <c r="EO12" t="n">
-        <v>4.368257577880286e-05</v>
+        <v>0.002965949941426516</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0001042201110976748</v>
+        <v>0.008361048996448517</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001334457192569971</v>
+        <v>0.002655017655342817</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001554163900436834</v>
+        <v>0.005249736830592155</v>
       </c>
       <c r="ES12" t="n">
-        <v>6.048800423741341e-05</v>
+        <v>0.006754779256880283</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0001966887502931058</v>
+        <v>0.009398192167282104</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0001422098866896704</v>
+        <v>0.002194348722696304</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0002619430888444185</v>
+        <v>0.000391942507121712</v>
       </c>
       <c r="EW12" t="n">
-        <v>5.336994217941537e-05</v>
+        <v>0.001917108776979148</v>
       </c>
       <c r="EX12" t="n">
-        <v>5.828135181218386e-05</v>
+        <v>0.0007506835390813649</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0002111710928147659</v>
+        <v>0.01197544857859612</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0001042448639054783</v>
+        <v>0.003356171771883965</v>
       </c>
       <c r="FA12" t="n">
-        <v>5.717070598620921e-05</v>
+        <v>0.005877763032913208</v>
       </c>
       <c r="FB12" t="n">
-        <v>4.964388426742516e-05</v>
+        <v>0.000903288833796978</v>
       </c>
       <c r="FC12" t="n">
-        <v>4.557760621537454e-05</v>
+        <v>0.005699330009520054</v>
       </c>
       <c r="FD12" t="n">
-        <v>8.314280421473086e-05</v>
+        <v>0.0009121020557358861</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0001354932901449502</v>
+        <v>0.000794422288890928</v>
       </c>
       <c r="FF12" t="n">
-        <v>7.210381590994075e-05</v>
+        <v>0.004285064060240984</v>
       </c>
       <c r="FG12" t="n">
-        <v>6.569868128281087e-05</v>
+        <v>0.004284283146262169</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.130351756728487e-05</v>
+        <v>0.0002538659609854221</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.000204478099476546</v>
+        <v>0.00685869250446558</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0001143027839134447</v>
+        <v>0.00294514512643218</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0001065230462700129</v>
+        <v>5.642138421535492e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0001495410542702302</v>
+        <v>0.01103018037974834</v>
       </c>
       <c r="FM12" t="n">
-        <v>6.078604201320559e-06</v>
+        <v>0.003921811934560537</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0001022393407765776</v>
+        <v>0.00890703871846199</v>
       </c>
       <c r="FO12" t="n">
-        <v>7.502325752284378e-05</v>
+        <v>0.02132498286664486</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0001868995896074921</v>
+        <v>0.0003418305423110723</v>
       </c>
       <c r="FQ12" t="n">
-        <v>2.495248190825805e-05</v>
+        <v>0.003219974227249622</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0002367871784372255</v>
+        <v>0.00110035203397274</v>
       </c>
       <c r="FS12" t="n">
-        <v>3.807336543104611e-05</v>
+        <v>0.003244993276894093</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0001447061513317749</v>
+        <v>0.008134212344884872</v>
       </c>
       <c r="FU12" t="n">
-        <v>6.609542469959706e-05</v>
+        <v>0.003486283589154482</v>
       </c>
       <c r="FV12" t="n">
-        <v>3.823870792984962e-05</v>
+        <v>0.00459055881947279</v>
       </c>
       <c r="FW12" t="n">
-        <v>1.530443114461377e-06</v>
+        <v>0.02384127303957939</v>
       </c>
       <c r="FX12" t="n">
-        <v>1.691376564849634e-05</v>
+        <v>0.002700160490348935</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0002291093696840107</v>
+        <v>0.001432353863492608</v>
       </c>
       <c r="FZ12" t="n">
-        <v>9.376340312883258e-05</v>
+        <v>0.0009813362266868353</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0001315207919105887</v>
+        <v>0.01584786176681519</v>
       </c>
       <c r="GB12" t="n">
-        <v>4.661342245526612e-05</v>
+        <v>0.00122493936214596</v>
       </c>
       <c r="GC12" t="n">
-        <v>4.06546205340419e-05</v>
+        <v>0.01546382717788219</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001466636313125491</v>
+        <v>0.007297397591173649</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0002653019037097692</v>
+        <v>0.005408594384789467</v>
       </c>
       <c r="GF12" t="n">
-        <v>3.391452992218547e-05</v>
+        <v>0.002502246294170618</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.000152897642692551</v>
+        <v>0.001661688787862659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0001249665656359866</v>
+        <v>8.527305972449994e-09</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003868176136165857</v>
+        <v>1.218767042843183e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>9.836276876740158e-05</v>
+        <v>4.470361858466276e-10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0006247262936085463</v>
+        <v>3.893769306984041e-09</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001497651799581945</v>
+        <v>3.373014312302303e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0004911727737635374</v>
+        <v>7.250302580530388e-09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001788444060366601</v>
+        <v>8.725774547357901e-10</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005417066859081388</v>
+        <v>6.757512771571328e-09</v>
       </c>
       <c r="I13" t="n">
-        <v>2.488811878720298e-05</v>
+        <v>5.921224399685343e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>3.765890141949058e-05</v>
+        <v>1.022926010563197e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>0.003379252506420016</v>
+        <v>1.366785795653414e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0006403201259672642</v>
+        <v>5.017251059058481e-10</v>
       </c>
       <c r="M13" t="n">
-        <v>3.880217991536483e-05</v>
+        <v>4.066126990664998e-09</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0009862065780907869</v>
+        <v>3.56796858724806e-09</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0006737833609804511</v>
+        <v>6.055218548794983e-09</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001403860806021839</v>
+        <v>2.029962448135691e-10</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001442421053070575</v>
+        <v>7.392531919947487e-09</v>
       </c>
       <c r="R13" t="n">
-        <v>3.168168041156605e-05</v>
+        <v>4.905283401690497e-10</v>
       </c>
       <c r="S13" t="n">
-        <v>3.705840208567679e-05</v>
+        <v>2.287760425545571e-09</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0004803587798960507</v>
+        <v>1.51178636276228e-09</v>
       </c>
       <c r="U13" t="n">
-        <v>7.85202719271183e-05</v>
+        <v>9.306432846578616e-10</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0004044164670631289</v>
+        <v>3.13256642847648e-10</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0007015583105385303</v>
+        <v>1.083836465021193e-09</v>
       </c>
       <c r="X13" t="n">
-        <v>0.000141356562380679</v>
+        <v>1.545450989404173e-09</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.002524166135117e-05</v>
+        <v>8.698752829161549e-11</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0006655477918684483</v>
+        <v>4.277482368308938e-09</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001770443341229111</v>
+        <v>2.842293955751529e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0002044109569396824</v>
+        <v>1.035204366672815e-09</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.011200745590031e-06</v>
+        <v>1.918087910723898e-09</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001038252958096564</v>
+        <v>2.951226152347886e-09</v>
       </c>
       <c r="AE13" t="n">
-        <v>5.316311217029579e-05</v>
+        <v>1.934027160643836e-09</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0002557969419285655</v>
+        <v>8.642021542826228e-10</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.943587504792958e-05</v>
+        <v>1.900652080166765e-09</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.297542520565912e-05</v>
+        <v>1.091496115712687e-09</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0001972133904928342</v>
+        <v>1.387904569050136e-09</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.000339683931088075</v>
+        <v>3.522835134717184e-09</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0006539238383993506</v>
+        <v>4.442531231774183e-09</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0004238486289978027</v>
+        <v>1.190225251690435e-09</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0001188211317639798</v>
+        <v>4.358383876024163e-09</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.100615165545605e-05</v>
+        <v>1.640637070643436e-09</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0004385246429592371</v>
+        <v>1.65822647280045e-10</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.000375264004105702</v>
+        <v>6.08311290228869e-10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.067332727368921e-06</v>
+        <v>6.246446693225494e-10</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001436168095096946</v>
+        <v>4.439867362648897e-10</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.912053504493088e-05</v>
+        <v>1.297188051418985e-10</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.355700391693972e-05</v>
+        <v>8.635766768350095e-09</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.002568322466686368</v>
+        <v>4.027113087445855e-10</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0003314708592370152</v>
+        <v>4.023245736561876e-09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0002425499260425568</v>
+        <v>2.210751581799286e-09</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0008904673741199076</v>
+        <v>8.144526830733412e-09</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0003942878101952374</v>
+        <v>8.980642340894462e-10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0002780619543045759</v>
+        <v>1.138777294684701e-09</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0001000538759399205</v>
+        <v>3.306121487689495e-10</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.740870645036921e-05</v>
+        <v>6.547458131223038e-10</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0004744438629131764</v>
+        <v>2.469703108687327e-09</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.000923574436455965</v>
+        <v>7.10667702463752e-09</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0005980835994705558</v>
+        <v>9.754663743422043e-11</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0001395020808558911</v>
+        <v>2.399838994193715e-09</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0006391920032911003</v>
+        <v>8.632839332278763e-09</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0003957330191042274</v>
+        <v>5.178000694883167e-09</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0003678200591821223</v>
+        <v>7.072656349471629e-10</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0002154509274987504</v>
+        <v>2.211251182160368e-09</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0001134665144491009</v>
+        <v>5.071209230322893e-09</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0003355027001816779</v>
+        <v>3.869925491173376e-10</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0007074463064782321</v>
+        <v>8.552655250682051e-10</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0003579319745767862</v>
+        <v>2.843611734970608e-10</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0001654216030146927</v>
+        <v>8.88635887097422e-10</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0004059695638716221</v>
+        <v>6.967128540757983e-10</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0002020283136516809</v>
+        <v>1.664834659020897e-10</v>
       </c>
       <c r="BR13" t="n">
-        <v>4.065080429427326e-05</v>
+        <v>1.621337397672562e-09</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0001159036037279293</v>
+        <v>1.237436930701108e-09</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001726977934595197</v>
+        <v>1.686278894297288e-09</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.891526234336197e-05</v>
+        <v>5.883903142489544e-09</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.001568268868140876</v>
+        <v>2.103654750396089e-10</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0002494979707989842</v>
+        <v>1.541981209385312e-09</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0001440394553355873</v>
+        <v>2.404387522414453e-10</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0004767325590364635</v>
+        <v>6.096863014448672e-10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0001882490905700251</v>
+        <v>8.163936193739119e-10</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0001822855265345424</v>
+        <v>1.258784187996298e-09</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.000142455828608945</v>
+        <v>2.130914333875467e-09</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0001074076644727029</v>
+        <v>1.199488730563303e-09</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0001107070711441338</v>
+        <v>1.471523458640434e-09</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.000606117770075798</v>
+        <v>2.97524760384249e-09</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001425347290933132</v>
+        <v>4.269915809818059e-10</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0001071679871529341</v>
+        <v>1.487847733905312e-09</v>
       </c>
       <c r="CH13" t="n">
-        <v>3.936531720682979e-05</v>
+        <v>1.629515189449648e-09</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.257724306924501e-05</v>
+        <v>2.654119590772552e-09</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0001754867262206972</v>
+        <v>3.686464744578899e-10</v>
       </c>
       <c r="CK13" t="n">
-        <v>9.86686791293323e-05</v>
+        <v>1.039489050391751e-09</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.778869409463368e-05</v>
+        <v>1.083545808633346e-09</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0008421585662290454</v>
+        <v>1.598829069138219e-09</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0005413807230070233</v>
+        <v>7.108089672414053e-10</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0002414977498119697</v>
+        <v>2.992480041541512e-09</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0001831045374274254</v>
+        <v>1.353840706208587e-09</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0004864432848989964</v>
+        <v>2.704519275198436e-09</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0003917122085113078</v>
+        <v>2.10938644329417e-09</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0006204526289366186</v>
+        <v>9.887630714189299e-10</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0004868296382483095</v>
+        <v>1.596425103222998e-09</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001204040090669878</v>
+        <v>2.136700594235208e-09</v>
       </c>
       <c r="CV13" t="n">
-        <v>9.1767986305058e-05</v>
+        <v>1.009202388324582e-09</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0004913857555948198</v>
+        <v>2.815180089044134e-09</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0002396461204625666</v>
+        <v>3.901781120418946e-10</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0002956481475848705</v>
+        <v>1.582355690921133e-09</v>
       </c>
       <c r="CZ13" t="n">
-        <v>7.333753455895931e-05</v>
+        <v>1.1331506843959e-09</v>
       </c>
       <c r="DA13" t="n">
-        <v>3.680675581563264e-05</v>
+        <v>2.451677971748722e-09</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001426751259714365</v>
+        <v>3.510977064635767e-10</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001769336085999385</v>
+        <v>1.95389082691122e-09</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.290769771207124e-05</v>
+        <v>1.233887325646776e-09</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0003477345744613558</v>
+        <v>1.054921927590158e-09</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0006204997189342976</v>
+        <v>5.21578469303563e-09</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.276839611819014e-05</v>
+        <v>4.80699258176287e-09</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.001365111558698118</v>
+        <v>1.737832544534967e-09</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.000622734718490392</v>
+        <v>4.721417035113973e-09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0002375525946263224</v>
+        <v>1.567962981674498e-09</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.000241104542510584</v>
+        <v>3.127649694789625e-09</v>
       </c>
       <c r="DL13" t="n">
-        <v>9.795719961402938e-05</v>
+        <v>8.962319775207561e-11</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0001864591467892751</v>
+        <v>3.260355985190699e-09</v>
       </c>
       <c r="DN13" t="n">
-        <v>5.405749834608287e-05</v>
+        <v>2.564585210862447e-09</v>
       </c>
       <c r="DO13" t="n">
-        <v>6.303676491370425e-05</v>
+        <v>3.750465271679104e-09</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.000366669031791389</v>
+        <v>1.681469408154612e-09</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002672391710802913</v>
+        <v>2.905604645775384e-09</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0002440823154756799</v>
+        <v>1.077398170679089e-09</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002537761174608022</v>
+        <v>1.078968359102817e-09</v>
       </c>
       <c r="DT13" t="n">
-        <v>4.942637679050677e-05</v>
+        <v>2.196136161813911e-09</v>
       </c>
       <c r="DU13" t="n">
-        <v>3.059209848288447e-05</v>
+        <v>2.084779682220983e-09</v>
       </c>
       <c r="DV13" t="n">
-        <v>3.024833495146595e-05</v>
+        <v>1.683725603385255e-09</v>
       </c>
       <c r="DW13" t="n">
-        <v>3.93405971408356e-05</v>
+        <v>2.390005970909215e-09</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0004156583163421601</v>
+        <v>9.847577198129898e-10</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0002078880788758397</v>
+        <v>1.988020859045037e-09</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.727030267938972e-06</v>
+        <v>3.792289815507388e-10</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0003609322884585708</v>
+        <v>6.907267646738546e-09</v>
       </c>
       <c r="EB13" t="n">
-        <v>4.631440242519602e-05</v>
+        <v>1.703888918846985e-09</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0001002766075544059</v>
+        <v>2.056040893094746e-09</v>
       </c>
       <c r="ED13" t="n">
-        <v>3.576544258976355e-05</v>
+        <v>1.998369913991382e-09</v>
       </c>
       <c r="EE13" t="n">
-        <v>2.640197271830402e-05</v>
+        <v>1.621787926175955e-09</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0003832211659755558</v>
+        <v>1.868452947917376e-09</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0006472521345131099</v>
+        <v>8.490261826921142e-10</v>
       </c>
       <c r="EH13" t="n">
-        <v>3.540120451361872e-05</v>
+        <v>1.830643636679952e-09</v>
       </c>
       <c r="EI13" t="n">
-        <v>1.282730227103457e-05</v>
+        <v>1.303735452928834e-10</v>
       </c>
       <c r="EJ13" t="n">
-        <v>4.619421088136733e-05</v>
+        <v>2.762244599718855e-11</v>
       </c>
       <c r="EK13" t="n">
-        <v>2.159756695618853e-05</v>
+        <v>1.999149068510064e-09</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001016468595480546</v>
+        <v>5.6489907196422e-10</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001358881127089262</v>
+        <v>8.586783506459028e-10</v>
       </c>
       <c r="EN13" t="n">
-        <v>3.283403202658519e-05</v>
+        <v>9.411632584388485e-10</v>
       </c>
       <c r="EO13" t="n">
-        <v>9.330290777143091e-05</v>
+        <v>4.363666095130725e-10</v>
       </c>
       <c r="EP13" t="n">
-        <v>5.421113746706396e-05</v>
+        <v>2.360510675813998e-09</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0004607366281561553</v>
+        <v>4.554902011122408e-10</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0003623258089646697</v>
+        <v>4.297081857007612e-10</v>
       </c>
       <c r="ES13" t="n">
-        <v>2.883210800064262e-05</v>
+        <v>2.629421569366741e-09</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.000149862389662303</v>
+        <v>2.55302468055163e-09</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0002211350365541875</v>
+        <v>1.358586576571952e-10</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0004465146630536765</v>
+        <v>1.573734698112617e-09</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0003069215454161167</v>
+        <v>3.777840262841892e-09</v>
       </c>
       <c r="EX13" t="n">
-        <v>6.902911991346627e-05</v>
+        <v>1.53182933004814e-09</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0005298923351801932</v>
+        <v>3.589375463519673e-09</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001857876632129773</v>
+        <v>9.495597363962105e-11</v>
       </c>
       <c r="FA13" t="n">
-        <v>5.650417369906791e-05</v>
+        <v>1.886355294189457e-09</v>
       </c>
       <c r="FB13" t="n">
-        <v>1.515471922175493e-06</v>
+        <v>1.792189618932127e-09</v>
       </c>
       <c r="FC13" t="n">
-        <v>8.809546125121415e-05</v>
+        <v>2.233726759115484e-09</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0002072813222184777</v>
+        <v>1.620055756212935e-10</v>
       </c>
       <c r="FE13" t="n">
-        <v>8.43853922560811e-05</v>
+        <v>2.095555950987205e-09</v>
       </c>
       <c r="FF13" t="n">
-        <v>4.25798752985429e-05</v>
+        <v>5.860369967081169e-10</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001139033847721294</v>
+        <v>6.228823568044106e-10</v>
       </c>
       <c r="FH13" t="n">
-        <v>2.313108052476309e-05</v>
+        <v>2.718750558017291e-09</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0003852691152133048</v>
+        <v>3.458699993075243e-09</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.000282667635474354</v>
+        <v>1.18027521089914e-09</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0003843445447273552</v>
+        <v>3.983597451906462e-09</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0001782843755790964</v>
+        <v>2.387896325117822e-09</v>
       </c>
       <c r="FM13" t="n">
-        <v>9.614053124096245e-05</v>
+        <v>1.184947140409065e-10</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001063381205312908</v>
+        <v>3.316011465415158e-09</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0002776558394543827</v>
+        <v>6.428504395472601e-10</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0003997875028289855</v>
+        <v>3.961002192909291e-09</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0005327918916009367</v>
+        <v>4.925776675435145e-09</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0004517521883826703</v>
+        <v>8.516439997663383e-09</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0001747551141306758</v>
+        <v>2.819688926791741e-09</v>
       </c>
       <c r="FT13" t="n">
-        <v>8.574272214900702e-06</v>
+        <v>2.20360307778833e-09</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0001349357335129753</v>
+        <v>1.446125552639899e-09</v>
       </c>
       <c r="FV13" t="n">
-        <v>9.410592610947788e-06</v>
+        <v>4.024406141667214e-09</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0001590175379533321</v>
+        <v>1.905616109354469e-09</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0001024590310407802</v>
+        <v>2.826948675149765e-09</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0005127167096361518</v>
+        <v>2.010105193406275e-09</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001963107060873881</v>
+        <v>3.558519257040871e-09</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0001022866053972393</v>
+        <v>3.77091380343586e-09</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001255335082532838</v>
+        <v>6.384114348279013e-10</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0002646413340698928</v>
+        <v>5.832595739718727e-09</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0006028456846252084</v>
+        <v>1.552571182728002e-09</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.000551949255168438</v>
+        <v>1.552900474877106e-09</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0002710141707211733</v>
+        <v>1.274005456686211e-09</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0002056869125226513</v>
+        <v>2.384840103175634e-09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5.408277502283454e-05</v>
+        <v>5.475449142977595e-06</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001144577981904149</v>
+        <v>0.007209243252873421</v>
       </c>
       <c r="C14" t="n">
-        <v>9.008905180962756e-05</v>
+        <v>0.0004114933544769883</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006947661750018597</v>
+        <v>0.00597032718360424</v>
       </c>
       <c r="E14" t="n">
-        <v>5.069307735539041e-05</v>
+        <v>0.00146239111199975</v>
       </c>
       <c r="F14" t="n">
-        <v>4.394125426188111e-06</v>
+        <v>0.008973400108516216</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001045923636411317</v>
+        <v>0.002945741172879934</v>
       </c>
       <c r="H14" t="n">
-        <v>6.168438994791359e-05</v>
+        <v>0.003712129546329379</v>
       </c>
       <c r="I14" t="n">
-        <v>9.638263145461679e-05</v>
+        <v>0.002952216425910592</v>
       </c>
       <c r="J14" t="n">
-        <v>6.067461072234437e-05</v>
+        <v>0.0004596076032612473</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0009694110485725105</v>
+        <v>0.008345644921064377</v>
       </c>
       <c r="L14" t="n">
-        <v>8.279030225821771e-06</v>
+        <v>0.001920708455145359</v>
       </c>
       <c r="M14" t="n">
-        <v>0.000673311878927052</v>
+        <v>0.007582433521747589</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0001623217685846612</v>
+        <v>0.002662214683368802</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0001244851591764018</v>
+        <v>0.009736546315252781</v>
       </c>
       <c r="P14" t="n">
-        <v>6.872281664982438e-05</v>
+        <v>0.001449732226319611</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001188285095850006</v>
+        <v>0.003032924374565482</v>
       </c>
       <c r="R14" t="n">
-        <v>3.286716673756018e-05</v>
+        <v>0.001430449308827519</v>
       </c>
       <c r="S14" t="n">
-        <v>9.661237709224224e-05</v>
+        <v>0.0001840378681663424</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0001157778679043986</v>
+        <v>0.0002259340835735202</v>
       </c>
       <c r="U14" t="n">
-        <v>4.814170461031608e-05</v>
+        <v>0.0008476085495203733</v>
       </c>
       <c r="V14" t="n">
-        <v>6.986539665376768e-05</v>
+        <v>0.0006773952627554536</v>
       </c>
       <c r="W14" t="n">
-        <v>5.002252510166727e-05</v>
+        <v>0.0004590578028000891</v>
       </c>
       <c r="X14" t="n">
-        <v>6.906525959493592e-05</v>
+        <v>0.001579598872922361</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.224587120115757e-05</v>
+        <v>0.001133210957050323</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001025473902700469</v>
+        <v>0.001453119795769453</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.509566785302013e-05</v>
+        <v>0.0004019976768177003</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001440609194105491</v>
+        <v>0.000633592251688242</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0002688619133550674</v>
+        <v>0.0007083053351379931</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.776504152279813e-05</v>
+        <v>0.001352379214949906</v>
       </c>
       <c r="AE14" t="n">
-        <v>5.474582212627865e-05</v>
+        <v>0.0009975482244044542</v>
       </c>
       <c r="AF14" t="n">
-        <v>7.280113641172647e-05</v>
+        <v>0.0001455873134545982</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.778182195266709e-06</v>
+        <v>0.00310291675850749</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.581076740985736e-05</v>
+        <v>0.0002023826236836612</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.272869889769936e-06</v>
+        <v>0.003621244570240378</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.876088936114684e-05</v>
+        <v>0.000107829189801123</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.004842488327995e-06</v>
+        <v>0.0005219306331127882</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001026326499413699</v>
+        <v>0.001017460133880377</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.369584737811238e-05</v>
+        <v>0.001233381452038884</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.904312375700101e-05</v>
+        <v>0.001204732805490494</v>
       </c>
       <c r="AO14" t="n">
-        <v>9.567470988258719e-05</v>
+        <v>0.0001519261277280748</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.688267214689404e-05</v>
+        <v>0.0003320709511172026</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.107147343456745e-05</v>
+        <v>0.0001120546949096024</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.750701216631569e-05</v>
+        <v>0.0005789260612800717</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.97563276742585e-05</v>
+        <v>0.0007751616649329662</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0001280878495890647</v>
+        <v>0.001206497428938746</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0007529962458647788</v>
+        <v>0.00335434777662158</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.000147232145536691</v>
+        <v>0.001643773051910102</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0002528811746742576</v>
+        <v>0.002658159472048283</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.092340067378245e-06</v>
+        <v>0.006672651972621679</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.307084110332653e-05</v>
+        <v>0.00515531562268734</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.540968464221805e-06</v>
+        <v>0.0001600277610123158</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.049924660241231e-05</v>
+        <v>0.0009359533432871103</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.778729362442391e-06</v>
+        <v>0.0005625407793559134</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.900441414676607e-05</v>
+        <v>0.0002489418548066169</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0001844162325141951</v>
+        <v>0.002375805051997304</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0002372921298956499</v>
+        <v>0.001409887801855803</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0001060095382854342</v>
+        <v>0.00110958400182426</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.390039485879242e-05</v>
+        <v>0.004060546401888132</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0001248042972292751</v>
+        <v>0.001664391485974193</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0001006188394967467</v>
+        <v>0.0009267404675483704</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.555040014674887e-05</v>
+        <v>0.003954239655286074</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.926192948711105e-05</v>
+        <v>0.001278188545256853</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001037265319610015</v>
+        <v>0.0002286445087520406</v>
       </c>
       <c r="BM14" t="n">
-        <v>7.688572077313438e-05</v>
+        <v>0.0002592967357486486</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0001340703893220052</v>
+        <v>6.683371611870825e-05</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.504306939954404e-05</v>
+        <v>0.001899833790957928</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0001828768581617624</v>
+        <v>5.309397238306701e-06</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.355937951710075e-05</v>
+        <v>0.001466049114242196</v>
       </c>
       <c r="BR14" t="n">
-        <v>7.222055864986032e-05</v>
+        <v>0.0002833491307683289</v>
       </c>
       <c r="BS14" t="n">
-        <v>3.513916453812271e-05</v>
+        <v>0.001849440857768059</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.354720244416967e-05</v>
+        <v>0.001147749368101358</v>
       </c>
       <c r="BU14" t="n">
-        <v>9.321197285316885e-05</v>
+        <v>0.0005301135824993253</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0003723172703757882</v>
+        <v>0.001767890062183142</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.58103487896733e-05</v>
+        <v>0.0008477560477331281</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0001467454567318782</v>
+        <v>0.002416204195469618</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.746939031174406e-05</v>
+        <v>0.001816174597479403</v>
       </c>
       <c r="BZ14" t="n">
-        <v>8.03125585662201e-05</v>
+        <v>0.002727333921939135</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.184370507369749e-05</v>
+        <v>0.001540685771033168</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.852493344107643e-05</v>
+        <v>8.338101906701922e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.956523116561584e-05</v>
+        <v>0.000819340581074357</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.779551348590758e-05</v>
+        <v>0.0002332021831534803</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0002104489394696429</v>
+        <v>0.002096600830554962</v>
       </c>
       <c r="CF14" t="n">
-        <v>4.779360097018071e-05</v>
+        <v>9.61163459578529e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>8.778316987445578e-05</v>
+        <v>0.002067075576633215</v>
       </c>
       <c r="CH14" t="n">
-        <v>5.037145820097066e-05</v>
+        <v>0.0002426754217594862</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.628284164529759e-06</v>
+        <v>0.002367845736443996</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.758344453468453e-05</v>
+        <v>2.237051376141608e-05</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.210764730785741e-05</v>
+        <v>0.0005129748024046421</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.865256490418687e-05</v>
+        <v>0.001095582963898778</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0002451503823976964</v>
+        <v>0.0001716430415399373</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0001330024970229715</v>
+        <v>0.0005045714206062257</v>
       </c>
       <c r="CO14" t="n">
-        <v>2.543839218560606e-05</v>
+        <v>0.002867648145183921</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0001797659060684964</v>
+        <v>0.002074587158858776</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0001986244751606137</v>
+        <v>0.003257209900766611</v>
       </c>
       <c r="CR14" t="n">
-        <v>8.762424840824679e-05</v>
+        <v>0.0009218968916684389</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0001025521123665385</v>
+        <v>0.0005358793423511088</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0001970319863175973</v>
+        <v>0.0006762837874703109</v>
       </c>
       <c r="CU14" t="n">
-        <v>6.278410182858352e-06</v>
+        <v>0.0007428426761180162</v>
       </c>
       <c r="CV14" t="n">
-        <v>7.947517588036135e-06</v>
+        <v>0.0003439023275859654</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0002094082883559167</v>
+        <v>0.001969421748071909</v>
       </c>
       <c r="CX14" t="n">
-        <v>8.124487794702873e-05</v>
+        <v>0.0002467101148795336</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0001181604893645272</v>
+        <v>0.002285072114318609</v>
       </c>
       <c r="CZ14" t="n">
-        <v>5.459087697090581e-05</v>
+        <v>0.0005040469695813954</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.426704122626688e-05</v>
+        <v>0.002502718241885304</v>
       </c>
       <c r="DB14" t="n">
-        <v>3.048015605600085e-05</v>
+        <v>0.0002044757129624486</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.07816392503446e-05</v>
+        <v>0.000410553504480049</v>
       </c>
       <c r="DD14" t="n">
-        <v>5.655311724694911e-06</v>
+        <v>0.0007739789434708655</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001391454425174743</v>
+        <v>0.0004011738346889615</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.260542482370511e-05</v>
+        <v>0.001808445900678635</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.133553011342883e-05</v>
+        <v>0.002614437602460384</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.000213533901842311</v>
+        <v>0.0009232634329237044</v>
       </c>
       <c r="DI14" t="n">
-        <v>5.458637315314263e-05</v>
+        <v>0.001593678258359432</v>
       </c>
       <c r="DJ14" t="n">
-        <v>9.841154678724706e-06</v>
+        <v>0.00248977611772716</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.336417648824863e-06</v>
+        <v>0.0002860409731511027</v>
       </c>
       <c r="DL14" t="n">
-        <v>7.405684300465509e-05</v>
+        <v>0.001663260278292</v>
       </c>
       <c r="DM14" t="n">
-        <v>5.503986903931946e-05</v>
+        <v>0.001266476465389132</v>
       </c>
       <c r="DN14" t="n">
-        <v>3.288207881269045e-05</v>
+        <v>0.0008136248216032982</v>
       </c>
       <c r="DO14" t="n">
-        <v>5.450794560601935e-05</v>
+        <v>0.002140191849321127</v>
       </c>
       <c r="DP14" t="n">
-        <v>8.370215073227882e-05</v>
+        <v>0.00128638930618763</v>
       </c>
       <c r="DQ14" t="n">
-        <v>4.914311648462899e-05</v>
+        <v>0.001307280035689473</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0001187483430840075</v>
+        <v>0.0002146101032849401</v>
       </c>
       <c r="DS14" t="n">
-        <v>1.548311593069229e-05</v>
+        <v>0.0009489060612395406</v>
       </c>
       <c r="DT14" t="n">
-        <v>3.700768138514832e-05</v>
+        <v>0.001088219694793224</v>
       </c>
       <c r="DU14" t="n">
-        <v>3.931271567125805e-05</v>
+        <v>0.00187591603025794</v>
       </c>
       <c r="DV14" t="n">
-        <v>5.714667349820957e-05</v>
+        <v>0.001636137720197439</v>
       </c>
       <c r="DW14" t="n">
-        <v>5.510651317308657e-05</v>
+        <v>0.0006125220097601414</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001728328206809238</v>
+        <v>0.000900211394764483</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.485156750888564e-06</v>
+        <v>0.001481007668189704</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.930225547170267e-05</v>
+        <v>0.0005635982379317284</v>
       </c>
       <c r="EA14" t="n">
-        <v>8.215229900088161e-05</v>
+        <v>0.0007189686875790358</v>
       </c>
       <c r="EB14" t="n">
-        <v>4.11438086302951e-05</v>
+        <v>0.0006004640599712729</v>
       </c>
       <c r="EC14" t="n">
-        <v>5.013807458453812e-05</v>
+        <v>0.0004912091535516083</v>
       </c>
       <c r="ED14" t="n">
-        <v>3.238062345189974e-05</v>
+        <v>0.002290863776579499</v>
       </c>
       <c r="EE14" t="n">
-        <v>1.787780274753459e-05</v>
+        <v>0.001957651926204562</v>
       </c>
       <c r="EF14" t="n">
-        <v>1.017374597722664e-05</v>
+        <v>7.645630103070289e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0001916957553476095</v>
+        <v>0.001619418384507298</v>
       </c>
       <c r="EH14" t="n">
-        <v>8.545852324459702e-05</v>
+        <v>0.001449144328944385</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001491655712015927</v>
+        <v>0.001117801177315414</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0001380762550979853</v>
+        <v>0.001073490595445037</v>
       </c>
       <c r="EK14" t="n">
-        <v>4.005398295703344e-06</v>
+        <v>0.002052785130217671</v>
       </c>
       <c r="EL14" t="n">
-        <v>2.095560557791032e-05</v>
+        <v>0.0004391200200188905</v>
       </c>
       <c r="EM14" t="n">
-        <v>3.199244747520424e-05</v>
+        <v>0.0008773732115514576</v>
       </c>
       <c r="EN14" t="n">
-        <v>1.641512972128112e-05</v>
+        <v>0.0005498949903994799</v>
       </c>
       <c r="EO14" t="n">
-        <v>7.316655683098361e-06</v>
+        <v>0.0007421124028041959</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0002431073226034641</v>
+        <v>0.001663394388742745</v>
       </c>
       <c r="EQ14" t="n">
-        <v>8.969190093921497e-05</v>
+        <v>0.0009446869371458888</v>
       </c>
       <c r="ER14" t="n">
-        <v>5.141478322912008e-05</v>
+        <v>0.002209713216871023</v>
       </c>
       <c r="ES14" t="n">
-        <v>3.195879253325984e-05</v>
+        <v>0.001066897995769978</v>
       </c>
       <c r="ET14" t="n">
-        <v>1.931770020746626e-05</v>
+        <v>0.0001642657734919339</v>
       </c>
       <c r="EU14" t="n">
-        <v>6.526082142954692e-05</v>
+        <v>0.0004400578327476978</v>
       </c>
       <c r="EV14" t="n">
-        <v>1.792196417227387e-05</v>
+        <v>0.0006878377171233296</v>
       </c>
       <c r="EW14" t="n">
-        <v>4.453399014892057e-05</v>
+        <v>0.00162464112509042</v>
       </c>
       <c r="EX14" t="n">
-        <v>3.679354631458409e-05</v>
+        <v>0.0003025837359018624</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0002170478401239961</v>
+        <v>0.002520188223570585</v>
       </c>
       <c r="EZ14" t="n">
-        <v>4.544567127595656e-05</v>
+        <v>3.604738594731316e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>9.703264367999509e-05</v>
+        <v>0.002418260555714369</v>
       </c>
       <c r="FB14" t="n">
-        <v>3.322424890939146e-05</v>
+        <v>0.0001109361037379131</v>
       </c>
       <c r="FC14" t="n">
-        <v>2.489359576429706e-05</v>
+        <v>0.002173896413296461</v>
       </c>
       <c r="FD14" t="n">
-        <v>2.113794835167937e-05</v>
+        <v>1.076870830729604e-06</v>
       </c>
       <c r="FE14" t="n">
-        <v>1.768958100001328e-06</v>
+        <v>0.0004513089661486447</v>
       </c>
       <c r="FF14" t="n">
-        <v>1.292607157665771e-05</v>
+        <v>0.0004487551341298968</v>
       </c>
       <c r="FG14" t="n">
-        <v>3.751036638277583e-05</v>
+        <v>0.0001382965128868818</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.000140382515382953</v>
+        <v>0.001197111210785806</v>
       </c>
       <c r="FI14" t="n">
-        <v>7.408091187244281e-05</v>
+        <v>0.002588902832940221</v>
       </c>
       <c r="FJ14" t="n">
-        <v>5.688206510967575e-05</v>
+        <v>0.002074936404824257</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0001003846264211461</v>
+        <v>0.0005882225232198834</v>
       </c>
       <c r="FL14" t="n">
-        <v>4.422290294314735e-05</v>
+        <v>0.002624577842652798</v>
       </c>
       <c r="FM14" t="n">
-        <v>6.233585008885711e-05</v>
+        <v>0.0001111890451284125</v>
       </c>
       <c r="FN14" t="n">
-        <v>5.101818169350736e-05</v>
+        <v>0.001809860463254154</v>
       </c>
       <c r="FO14" t="n">
-        <v>1.310609877691604e-05</v>
+        <v>0.002066230634227395</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001237559772562236</v>
+        <v>0.0009102160693146288</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0001290381042053923</v>
+        <v>0.0003839939599856734</v>
       </c>
       <c r="FR14" t="n">
-        <v>9.953112021321431e-05</v>
+        <v>0.004291885066777468</v>
       </c>
       <c r="FS14" t="n">
-        <v>6.117014709161595e-05</v>
+        <v>0.0001065130127244629</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001062958617694676</v>
+        <v>0.0009037568233907223</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0001173694327007979</v>
+        <v>0.001121725421398878</v>
       </c>
       <c r="FV14" t="n">
-        <v>3.559636388672516e-05</v>
+        <v>0.00056970224250108</v>
       </c>
       <c r="FW14" t="n">
-        <v>6.148120883153751e-05</v>
+        <v>0.001715675345622003</v>
       </c>
       <c r="FX14" t="n">
-        <v>3.437186751398258e-05</v>
+        <v>0.001949927071109414</v>
       </c>
       <c r="FY14" t="n">
-        <v>8.293368591694161e-05</v>
+        <v>0.0006910819793120027</v>
       </c>
       <c r="FZ14" t="n">
-        <v>5.901184340473264e-05</v>
+        <v>0.001687851967290044</v>
       </c>
       <c r="GA14" t="n">
-        <v>3.358396497787908e-05</v>
+        <v>0.002377742901444435</v>
       </c>
       <c r="GB14" t="n">
-        <v>5.542150029214099e-05</v>
+        <v>0.0006850589998066425</v>
       </c>
       <c r="GC14" t="n">
-        <v>3.633194137364626e-05</v>
+        <v>0.004138852935284376</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001386779767926782</v>
+        <v>0.00383151788264513</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0001559835800435394</v>
+        <v>0.0007437053136527538</v>
       </c>
       <c r="GF14" t="n">
-        <v>5.881403922103345e-05</v>
+        <v>0.0002825551782734692</v>
       </c>
       <c r="GG14" t="n">
-        <v>9.901988232741132e-05</v>
+        <v>0.0004257845575921237</v>
       </c>
     </row>
     <row r="15">
@@ -8965,571 +8965,571 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.550500201119576e-05</v>
+        <v>0.05168557912111282</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0005127161275595427</v>
+        <v>0.6011913418769836</v>
       </c>
       <c r="C16" t="n">
-        <v>6.337924787658267e-06</v>
+        <v>0.02656630240380764</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001516618358436972</v>
+        <v>0.1775253415107727</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0001039557319018058</v>
+        <v>0.1990625411272049</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002040562249021605</v>
+        <v>0.009934328496456146</v>
       </c>
       <c r="G16" t="n">
-        <v>5.863129990757443e-05</v>
+        <v>0.04839101806282997</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0001654067600611597</v>
+        <v>0.08680093288421631</v>
       </c>
       <c r="I16" t="n">
-        <v>7.21042015356943e-05</v>
+        <v>0.07341671735048294</v>
       </c>
       <c r="J16" t="n">
-        <v>8.453101327177137e-05</v>
+        <v>0.02415493130683899</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000461853458546102</v>
+        <v>0.7532019019126892</v>
       </c>
       <c r="L16" t="n">
-        <v>4.308296047383919e-05</v>
+        <v>0.06872817128896713</v>
       </c>
       <c r="M16" t="n">
-        <v>5.423289985628799e-05</v>
+        <v>0.2973628640174866</v>
       </c>
       <c r="N16" t="n">
-        <v>5.222506842983421e-06</v>
+        <v>0.004954829812049866</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0002077783283311874</v>
+        <v>0.01980531215667725</v>
       </c>
       <c r="P16" t="n">
-        <v>8.164947212208062e-05</v>
+        <v>0.0001979470252990723</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.28352858661674e-06</v>
+        <v>0.1379066854715347</v>
       </c>
       <c r="R16" t="n">
-        <v>9.726442658575252e-05</v>
+        <v>0.06884324550628662</v>
       </c>
       <c r="S16" t="n">
-        <v>1.385243649565382e-05</v>
+        <v>0.03502894565463066</v>
       </c>
       <c r="T16" t="n">
-        <v>4.34410831076093e-05</v>
+        <v>0.09738644957542419</v>
       </c>
       <c r="U16" t="n">
-        <v>3.263719554524869e-05</v>
+        <v>0.05015347525477409</v>
       </c>
       <c r="V16" t="n">
-        <v>5.444062844617292e-05</v>
+        <v>0.08904401957988739</v>
       </c>
       <c r="W16" t="n">
-        <v>7.546448614448309e-05</v>
+        <v>0.07238367944955826</v>
       </c>
       <c r="X16" t="n">
-        <v>4.873979196418077e-05</v>
+        <v>0.01762713119387627</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.223785461159423e-05</v>
+        <v>0.0786491259932518</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.479009218513966e-05</v>
+        <v>0.1703144162893295</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.217615398578346e-05</v>
+        <v>0.02993478253483772</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85219178092666e-05</v>
+        <v>0.00294961966574192</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.864547968783882e-05</v>
+        <v>0.0195755623281002</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.46150331501849e-05</v>
+        <v>0.1255358159542084</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.137517301685875e-05</v>
+        <v>0.2178937196731567</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.098430897807702e-05</v>
+        <v>0.1654509305953979</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.695594386954326e-06</v>
+        <v>0.02598021924495697</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.238929326063953e-05</v>
+        <v>0.02498956955969334</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.594977483269759e-05</v>
+        <v>0.1668076813220978</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.823877705144696e-06</v>
+        <v>0.06619276106357574</v>
       </c>
       <c r="AK16" t="n">
-        <v>6.711645983159542e-05</v>
+        <v>0.1000049859285355</v>
       </c>
       <c r="AL16" t="n">
-        <v>7.233830547193065e-05</v>
+        <v>0.09627345949411392</v>
       </c>
       <c r="AM16" t="n">
-        <v>8.763240657572169e-07</v>
+        <v>0.08127546310424805</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.026990088983439e-05</v>
+        <v>0.06841091066598892</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.790449101070408e-06</v>
+        <v>0.01305397227406502</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.780272426316515e-05</v>
+        <v>0.004937093704938889</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.534564893925563e-05</v>
+        <v>0.09206630289554596</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.308145824121311e-05</v>
+        <v>0.1968380212783813</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.850791421835311e-05</v>
+        <v>0.03878490999341011</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.11060068977531e-06</v>
+        <v>0.1813680529594421</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0003038653521798551</v>
+        <v>0.5042177438735962</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.091091952635907e-05</v>
+        <v>0.07868832349777222</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.984075712854974e-05</v>
+        <v>0.2220492362976074</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.034021498635411e-05</v>
+        <v>0.2516067028045654</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0001337895228061825</v>
+        <v>0.0773124098777771</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0001140639142249711</v>
+        <v>0.02784054167568684</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.366867016069591e-05</v>
+        <v>0.06191462278366089</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.217942715622485e-05</v>
+        <v>0.07321999967098236</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.515677912626415e-06</v>
+        <v>0.1418801993131638</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0001148059964179993</v>
+        <v>0.0328940711915493</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.000111396650027018</v>
+        <v>0.05965974554419518</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.098389035789296e-05</v>
+        <v>0.02031303942203522</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.821465750457719e-05</v>
+        <v>0.06623611599206924</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.131209763931111e-05</v>
+        <v>0.03050932660698891</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.04457314289175e-05</v>
+        <v>0.18305703997612</v>
       </c>
       <c r="BJ16" t="n">
-        <v>7.937414920888841e-05</v>
+        <v>0.1694552898406982</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.564881186932325e-05</v>
+        <v>0.08052337914705276</v>
       </c>
       <c r="BL16" t="n">
-        <v>2.923755710071418e-05</v>
+        <v>0.06252489984035492</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.302226418280043e-05</v>
+        <v>0.04824116080999374</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.144297392689623e-05</v>
+        <v>0.04894037544727325</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.097095057251863e-05</v>
+        <v>0.0699533224105835</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.34138097363757e-06</v>
+        <v>0.1600662022829056</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.747930557234213e-05</v>
+        <v>0.0002505570009816438</v>
       </c>
       <c r="BR16" t="n">
-        <v>6.072054384276271e-05</v>
+        <v>0.1828694939613342</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.359173595323227e-05</v>
+        <v>0.07555840164422989</v>
       </c>
       <c r="BT16" t="n">
-        <v>1.286608494410757e-05</v>
+        <v>0.12154620885849</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.478342816582881e-06</v>
+        <v>0.08741423487663269</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0001835147850215435</v>
+        <v>0.3046643137931824</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.831232167314738e-05</v>
+        <v>0.09792131185531616</v>
       </c>
       <c r="BX16" t="n">
-        <v>4.874527803622186e-06</v>
+        <v>0.1002838611602783</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.175885260337964e-05</v>
+        <v>0.02649367228150368</v>
       </c>
       <c r="BZ16" t="n">
-        <v>5.938156027696095e-05</v>
+        <v>0.002091461792588234</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.064586391905323e-07</v>
+        <v>0.1288148015737534</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.380634941800963e-05</v>
+        <v>0.06010345369577408</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.062912871129811e-05</v>
+        <v>0.03837532922625542</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.333895049057901e-06</v>
+        <v>0.0134234856814146</v>
       </c>
       <c r="CE16" t="n">
-        <v>9.143551869783551e-05</v>
+        <v>0.1918596476316452</v>
       </c>
       <c r="CF16" t="n">
-        <v>4.460943819140084e-05</v>
+        <v>0.01709822192788124</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.722478348005097e-05</v>
+        <v>0.0236321147531271</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5124591300264e-05</v>
+        <v>0.01950725913047791</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.248045191459823e-05</v>
+        <v>0.01868217810988426</v>
       </c>
       <c r="CJ16" t="n">
-        <v>3.460405423538759e-05</v>
+        <v>0.02357287704944611</v>
       </c>
       <c r="CK16" t="n">
-        <v>2.234468774986453e-05</v>
+        <v>0.03947960957884789</v>
       </c>
       <c r="CL16" t="n">
-        <v>4.904501838609576e-05</v>
+        <v>0.007615658454596996</v>
       </c>
       <c r="CM16" t="n">
-        <v>6.316610233625397e-05</v>
+        <v>0.02533257938921452</v>
       </c>
       <c r="CN16" t="n">
-        <v>5.410677840700373e-05</v>
+        <v>0.1418206244707108</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.369095298286993e-05</v>
+        <v>0.06863545626401901</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0001347056968370453</v>
+        <v>0.1206311583518982</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.840496644144878e-05</v>
+        <v>0.124967947602272</v>
       </c>
       <c r="CR16" t="n">
-        <v>6.915810809005052e-05</v>
+        <v>0.01928186044096947</v>
       </c>
       <c r="CS16" t="n">
-        <v>9.991737169912085e-05</v>
+        <v>0.1441674530506134</v>
       </c>
       <c r="CT16" t="n">
-        <v>6.914306140970439e-05</v>
+        <v>0.08244511485099792</v>
       </c>
       <c r="CU16" t="n">
-        <v>3.706922143464908e-05</v>
+        <v>0.04664375633001328</v>
       </c>
       <c r="CV16" t="n">
-        <v>4.805613116332097e-06</v>
+        <v>0.03250417858362198</v>
       </c>
       <c r="CW16" t="n">
-        <v>8.137537952279672e-05</v>
+        <v>0.1771021485328674</v>
       </c>
       <c r="CX16" t="n">
-        <v>4.979349614586681e-05</v>
+        <v>0.02907192148268223</v>
       </c>
       <c r="CY16" t="n">
-        <v>5.326647806214169e-05</v>
+        <v>0.06658336520195007</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.218765075667761e-05</v>
+        <v>0.05906595289707184</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.267427796847187e-05</v>
+        <v>0.03125095367431641</v>
       </c>
       <c r="DB16" t="n">
-        <v>3.727547300513834e-05</v>
+        <v>6.125494837760925e-05</v>
       </c>
       <c r="DC16" t="n">
-        <v>4.259499837644398e-05</v>
+        <v>0.03564213588833809</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.313770841690712e-05</v>
+        <v>0.02171437814831734</v>
       </c>
       <c r="DE16" t="n">
-        <v>4.709084532805718e-05</v>
+        <v>0.02150282263755798</v>
       </c>
       <c r="DF16" t="n">
-        <v>8.267715747933835e-05</v>
+        <v>0.04203056544065475</v>
       </c>
       <c r="DG16" t="n">
-        <v>5.540507117984816e-06</v>
+        <v>0.02972458675503731</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0002361258084420115</v>
+        <v>0.09615409374237061</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0001252373185707256</v>
+        <v>0.3227706849575043</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0001785626373020932</v>
+        <v>0.06977637112140656</v>
       </c>
       <c r="DK16" t="n">
-        <v>7.847024244256318e-05</v>
+        <v>0.03392781317234039</v>
       </c>
       <c r="DL16" t="n">
-        <v>8.302400965476409e-05</v>
+        <v>0.113826647400856</v>
       </c>
       <c r="DM16" t="n">
-        <v>7.895268936408684e-05</v>
+        <v>0.1813711225986481</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.19997873500688e-05</v>
+        <v>0.0459730327129364</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.492371615720913e-05</v>
+        <v>0.02441104501485825</v>
       </c>
       <c r="DP16" t="n">
-        <v>4.08498672186397e-05</v>
+        <v>0.02043340913951397</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.452378364774631e-05</v>
+        <v>0.05504104495048523</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.696282409597188e-06</v>
+        <v>0.119002491235733</v>
       </c>
       <c r="DS16" t="n">
-        <v>3.262631798861548e-05</v>
+        <v>0.06268221139907837</v>
       </c>
       <c r="DT16" t="n">
-        <v>4.44957877334673e-05</v>
+        <v>0.1785934269428253</v>
       </c>
       <c r="DU16" t="n">
-        <v>2.893889723054599e-05</v>
+        <v>0.02135967835783958</v>
       </c>
       <c r="DV16" t="n">
-        <v>2.481209412508179e-05</v>
+        <v>0.1387789696455002</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.562979196023662e-05</v>
+        <v>0.07930327206850052</v>
       </c>
       <c r="DX16" t="n">
-        <v>2.909154864028096e-05</v>
+        <v>0.02729667723178864</v>
       </c>
       <c r="DY16" t="n">
-        <v>5.810468428535387e-05</v>
+        <v>0.005595753435045481</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.435821054154076e-05</v>
+        <v>0.06998182088136673</v>
       </c>
       <c r="EA16" t="n">
-        <v>5.356703695724718e-06</v>
+        <v>0.006653457880020142</v>
       </c>
       <c r="EB16" t="n">
-        <v>3.168445618939586e-05</v>
+        <v>0.04270472377538681</v>
       </c>
       <c r="EC16" t="n">
-        <v>6.247513738344423e-06</v>
+        <v>0.04377730563282967</v>
       </c>
       <c r="ED16" t="n">
-        <v>2.282685454702005e-05</v>
+        <v>0.1910985261201859</v>
       </c>
       <c r="EE16" t="n">
-        <v>7.910808926681057e-05</v>
+        <v>0.1488259434700012</v>
       </c>
       <c r="EF16" t="n">
-        <v>2.399622280790936e-05</v>
+        <v>0.05794965103268623</v>
       </c>
       <c r="EG16" t="n">
-        <v>9.34709096327424e-05</v>
+        <v>0.1182228401303291</v>
       </c>
       <c r="EH16" t="n">
-        <v>1.443707515136339e-05</v>
+        <v>0.05707023665308952</v>
       </c>
       <c r="EI16" t="n">
-        <v>1.873192377388477e-05</v>
+        <v>0.0268856305629015</v>
       </c>
       <c r="EJ16" t="n">
-        <v>6.345194560708478e-05</v>
+        <v>0.06065090000629425</v>
       </c>
       <c r="EK16" t="n">
-        <v>3.368274337844923e-05</v>
+        <v>0.03226448595523834</v>
       </c>
       <c r="EL16" t="n">
-        <v>4.337088466854766e-05</v>
+        <v>0.04213003814220428</v>
       </c>
       <c r="EM16" t="n">
-        <v>3.571959496184718e-06</v>
+        <v>0.07599250227212906</v>
       </c>
       <c r="EN16" t="n">
-        <v>2.315322490176186e-05</v>
+        <v>0.04835078120231628</v>
       </c>
       <c r="EO16" t="n">
-        <v>1.101165253203362e-06</v>
+        <v>0.07180389016866684</v>
       </c>
       <c r="EP16" t="n">
-        <v>5.238272569840774e-05</v>
+        <v>0.09043675661087036</v>
       </c>
       <c r="EQ16" t="n">
-        <v>9.8613221780397e-05</v>
+        <v>0.005965039134025574</v>
       </c>
       <c r="ER16" t="n">
-        <v>9.846196189755574e-05</v>
+        <v>0.01951106265187263</v>
       </c>
       <c r="ES16" t="n">
-        <v>6.801622657803819e-05</v>
+        <v>0.0918264165520668</v>
       </c>
       <c r="ET16" t="n">
-        <v>2.138650415872689e-05</v>
+        <v>0.0007307045161724091</v>
       </c>
       <c r="EU16" t="n">
-        <v>9.631617285776883e-05</v>
+        <v>0.01781386509537697</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0001037563342833892</v>
+        <v>0.05448741093277931</v>
       </c>
       <c r="EW16" t="n">
-        <v>7.995271516847424e-06</v>
+        <v>0.003652847371995449</v>
       </c>
       <c r="EX16" t="n">
-        <v>1.623555817786837e-06</v>
+        <v>0.0009272657334804535</v>
       </c>
       <c r="EY16" t="n">
-        <v>7.884585647843778e-05</v>
+        <v>0.2062731832265854</v>
       </c>
       <c r="EZ16" t="n">
-        <v>3.979816028731875e-05</v>
+        <v>0.02065153233706951</v>
       </c>
       <c r="FA16" t="n">
-        <v>1.582194636284839e-05</v>
+        <v>0.0482037253677845</v>
       </c>
       <c r="FB16" t="n">
-        <v>3.052682586712763e-05</v>
+        <v>0.08056836575269699</v>
       </c>
       <c r="FC16" t="n">
-        <v>1.422074547008378e-05</v>
+        <v>0.01647572964429855</v>
       </c>
       <c r="FD16" t="n">
-        <v>6.408242916222662e-05</v>
+        <v>0.02763139829039574</v>
       </c>
       <c r="FE16" t="n">
-        <v>4.306792834540829e-05</v>
+        <v>0.03475558012723923</v>
       </c>
       <c r="FF16" t="n">
-        <v>5.967739707557485e-05</v>
+        <v>0.03393106162548065</v>
       </c>
       <c r="FG16" t="n">
-        <v>2.351411603740416e-05</v>
+        <v>0.03011824935674667</v>
       </c>
       <c r="FH16" t="n">
-        <v>1.828174845286412e-06</v>
+        <v>0.2264510691165924</v>
       </c>
       <c r="FI16" t="n">
-        <v>8.790862193563953e-05</v>
+        <v>0.01859267055988312</v>
       </c>
       <c r="FJ16" t="n">
-        <v>4.875326339970343e-05</v>
+        <v>0.1553203463554382</v>
       </c>
       <c r="FK16" t="n">
-        <v>1.437653918401338e-05</v>
+        <v>0.05266086012125015</v>
       </c>
       <c r="FL16" t="n">
-        <v>1.69077429745812e-05</v>
+        <v>0.07480037957429886</v>
       </c>
       <c r="FM16" t="n">
-        <v>4.077191624674015e-05</v>
+        <v>0.1669122278690338</v>
       </c>
       <c r="FN16" t="n">
-        <v>3.293580812169239e-05</v>
+        <v>0.07369296252727509</v>
       </c>
       <c r="FO16" t="n">
-        <v>4.139136945013888e-05</v>
+        <v>0.01179663091897964</v>
       </c>
       <c r="FP16" t="n">
-        <v>4.008326504845172e-05</v>
+        <v>0.09809864312410355</v>
       </c>
       <c r="FQ16" t="n">
-        <v>2.855907223420218e-05</v>
+        <v>0.1236151307821274</v>
       </c>
       <c r="FR16" t="n">
-        <v>7.860719779273495e-05</v>
+        <v>0.04526906460523605</v>
       </c>
       <c r="FS16" t="n">
-        <v>8.9776556706056e-05</v>
+        <v>0.01268695667386055</v>
       </c>
       <c r="FT16" t="n">
-        <v>7.26435609976761e-05</v>
+        <v>0.268320620059967</v>
       </c>
       <c r="FU16" t="n">
-        <v>3.845117316814139e-05</v>
+        <v>0.4108781218528748</v>
       </c>
       <c r="FV16" t="n">
-        <v>7.942298543639481e-05</v>
+        <v>0.08670045435428619</v>
       </c>
       <c r="FW16" t="n">
-        <v>3.632399966591038e-06</v>
+        <v>0.03294956311583519</v>
       </c>
       <c r="FX16" t="n">
-        <v>3.311339241918176e-05</v>
+        <v>0.008155852556228638</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0001021419302560389</v>
+        <v>0.1298279017210007</v>
       </c>
       <c r="FZ16" t="n">
-        <v>2.034310637100134e-05</v>
+        <v>0.007652627304196358</v>
       </c>
       <c r="GA16" t="n">
-        <v>5.030962347518653e-05</v>
+        <v>0.08649618178606033</v>
       </c>
       <c r="GB16" t="n">
-        <v>3.197345722583123e-05</v>
+        <v>0.003020565956830978</v>
       </c>
       <c r="GC16" t="n">
-        <v>2.05206852115225e-05</v>
+        <v>0.08036941289901733</v>
       </c>
       <c r="GD16" t="n">
-        <v>5.581208097282797e-05</v>
+        <v>0.01473275944590569</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0001436285092495382</v>
+        <v>0.1221966445446014</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.074353531294037e-05</v>
+        <v>0.003127872943878174</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.246677766175708e-05</v>
+        <v>0.0824502632021904</v>
       </c>
     </row>
   </sheetData>
